--- a/Embedding_Scores.xlsx
+++ b/Embedding_Scores.xlsx
@@ -413,18 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>participant_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Aggregiert</t>
+          <t>prompts_all</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -455,272 +455,4201 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Welchen Vorteil hätte Deutschland, wenn es keine Waffen an die Ukraine liefern würde?
-Gibt es in anderen europäischen Ländern auch einen Gesellschaftsdienst für junge Erwachsene und wie sind die Erfahrungen damit?
-Warum sind Leihmutterschaften in anderen Ländern erlaubt und in Deutschland verboten?</t>
+          <t>Was sind die pro- und Contrapunkte bei der Deutschen Waffenlieferung an die Ukraine. Begründe deine Aussagen. Was sagen Befürworter oder Gegner? In Deutschland wird diskutiert, ob es einen verpflichtenden Gesellschaftsdienst nach dem Schulabschluss geben soll. Gib mir die Vor- und Nachteile dessen und begründe dies. Kann solch ein Dienst gesetzlich durchgesetzt werden? Verifiziere deine Aussagen. Gib mir Vor- und Nachteile von Legalisierung der aktiven Sterbehilfe. Begründe deine Aussagen.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8125531673431396</v>
+        <v>0.7106769680976868</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7935754060745239</v>
+        <v>0.7589463591575623</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8021587133407593</v>
+        <v>0.7337626218795776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7740370035171509</v>
+        <v>0.7471857666969299</v>
       </c>
       <c r="G2" t="n">
-        <v>0.723659873008728</v>
+        <v>0.7200338244438171</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wie viel geld hat deutschland bereits für waffen an die ukraine investiert
-für was für ausrüstung wird das geld hauptsächlich ausgegeben
-welche anderen länder liefern noch waffen
-Wie viele jugendliche haben nach ihrem schulabschluss ein gapyear
-Gibt es einen personalmangel in der bundeswehr oder in dem sozialen dienst?
-Was ist eine leihmutterschaft
-Was sagen kinder aus leihmütterschaften zu ihrem lebensweg, gibt es dort konkrete berichte</t>
+          <t>Hey, erkläre mir bitte in welchem Unfang Deutschland (als Staat und als private Unternehmen ansäßig in Deutschland) Waffen an die Ukraine liefert. Wie viele Waffen und welche Waffen sind das? Warum braucht die Ukraine diese Waffen? Welche anderen Länder beteiligen sich an der militärischen Unterstützung der Ukraine? Welche Gründe sprechen gegen militärische Unterstützung in Form von Waffenlieferungen? Hey, welche Vor- und Nachteile hätte ein verpflichtender Gesellschaftsdienst für junge Menschen? Beachte dabei bitte folgende Akteur*innen-Gruppen: junge Menschen, ältere Menschen, Arbeitnehmer &amp; -geber, Sozialeinrichtungen, Gesundheitssystem, Militär. Welche anderen Gruppen könnten von einem Gesellschaftsdienst noch profitieren? Gibt es Länder, die einen verpflichtenden Dienst bereits eigneführt haben? Hey, A) erkläre mir bitte warum die aktive Sterbehilfe aktuell in Deutschland verboten ist. B) Welche Länder legalisieren diese und unter welchen Umständen? C) Was spricht gegen die Legalisierung? Beziehe dich u.a. auf die Debatte in Kanada zur aktiven Sterbehilfe für Kriegsveteraner</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8118374943733215</v>
+        <v>0.779885470867157</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7891194820404053</v>
+        <v>0.8013989925384521</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8156184554100037</v>
+        <v>0.7847828269004822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7709207534790039</v>
+        <v>0.7914549112319946</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7212627530097961</v>
+        <v>0.7741678357124329</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Erstelle mir eine Übersicht der Pro und Cons der Waffenlieferungen an die Ukraine.
-Beschreibe zusätzlich die Positionen der demokratischen Parteien im Bundestag zu diesem Thema.
-Liste mir Pro und Contra Argumente für eine Wiedereinführung der Wehrpflicht in Deutschland auf. Was sind die Positionen der demokratischen Parteien im Bundestag?
-Wie könnte das praktisch umgesetzt werden? Was ist mit Frauen?
-Was sind die Argumente für und gegen ein verpflichtendes soziales Jahr (mit der Option dieses bei der Bundeswehr zu machen? Wie könnte es praktisch umgesetzt werden?
-Liste mir Pro und Contra Argumente für die Leihmutterschaft auf.
-Was zeigen Untersuchungen aus Ländern in denen diese legal ist?
-Wie könnte eine Leihmutterschaft in Deutschland sinnvoll umgesetzt werden?</t>
+          <t>Wie diskutieren einzelne Medien darüber? Kannst du mir dazu Textpassagen heraussuchen? Bitte gebe die dazugehörige Quelle an. Nenne mir die Vor- und Nachteile für Deutschland und die Welt, wenn weiterhin Waffen geliefert werden. Kannst du mir die sozialen, ökologischen und militärischen Aufgaben, die auf mich zukommen könnten, nennen? Erläutere mir diese. Nenne mir die Vor- und Nachteile der Sterbehilfe.</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7887846231460571</v>
+        <v>0.6757175326347351</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8123412132263184</v>
+        <v>0.7131195068359375</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8094804286956787</v>
+        <v>0.7016441822052002</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7779834270477295</v>
+        <v>0.7019103169441223</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7032831311225891</v>
+        <v>0.6943036913871765</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bitte trage hauptargumente zum diskurs über leihmutterschaft in deutschland zusammen, welche pro und contra punkte gibt es?
-Ok also mMn ist eine Schwangerschaft eine so einschneidende körperliche Erfahrung, der Frauen sich bei Leihmutterschaft im Kapitalismus womöglich aussetzen würden, wenn sie sich in finanziell prekären verhältnissen befinden. Weil ärmere frauen aus ihrer Notlage heraus eher ihre Gesundheit und ihr Wohlbefinden aufs Spiel setzen müssten, wird daraus eine soziale ungleichheit befeuert. Das stört mich hauptsächlich an dem Thema. Aber wie realistisch und konkret ist die Debatte? Bitte ordne ein, wie wahrscheinlich es ist, dass leihmutterschaft in DE erlaubt wird
-Bitte beleuchte das Thema noch mal aus feministischer Sicht</t>
+          <t>Bitte fass die unterschiedlichen Meinungen im öffentlichen deutschen Diskurs über die Lieferung von deutschen Waffen und militärische Ausrüstung an die Ukraine zusammen. Was spricht für einen verpflichtenden Gesellschaftsdienst in Deutschland? Was spricht dagegen. Bitte bezieh dich auf die aktuelle gesellschaftliche Debatte und gib Quellenangaben Sollte aktive Sterbehilfe in Deutschland legalisiert werden? Gib mir ausführliche pro und contra Argumente. Bitte sei gründlich</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8853672742843628</v>
+        <v>0.7299182415008545</v>
       </c>
       <c r="D5" t="n">
-        <v>0.875737726688385</v>
+        <v>0.7649824023246765</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8726173639297485</v>
+        <v>0.7531861066818237</v>
       </c>
       <c r="F5" t="n">
-        <v>0.851075291633606</v>
+        <v>0.7587260007858276</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8219588994979858</v>
+        <v>0.7264810800552368</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bitte liste mir die wichtigsten Argumente für und gegen Deutschlands Waffenlieferungen an die Ukraine auf. Bitte probiere die Argumente möglichst ausgewogen aus den verschiedensten Einflussfeldern zu wählen.
-Ich bin ein 26-jähriger Student mit Kinderwunsch in circa 10 Jahren. Bitte informiere mich sowohl gesellschaftlich als auch mich persönlich betreffendn über die Vor und Nachteile eines verpflichtenden Wehrdienstes oder ein verpflichtender sozialer Dienst in Deutschland für junge Erwachsene.
-Bitte informiere mich ausgewogen zur potenziellen Leihmutterschaft in Deutschland. Lege einen Fokus darauf welche Vorstöße es dazu schon gibt und was die am kontrovers diskutierten Fragen in der Öffentlichkeit sind.</t>
+          <t>was bringen waffenlieferungen aus deutschland für die ukraine Gesellschaftsdienst für junge Menschen Umsetzbarkeit aktive sterbehilfe vor und nachteile in welchen ländern gibt es aktive sterbehilfe und wie wird diese umgesetzt? was sagen kritiker dazu?</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8249621391296387</v>
+        <v>0.7200230956077576</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8400360345840454</v>
+        <v>0.7494232654571533</v>
       </c>
       <c r="E6" t="n">
-        <v>0.839073121547699</v>
+        <v>0.7372118234634399</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8169068098068237</v>
+        <v>0.7399594783782959</v>
       </c>
       <c r="G6" t="n">
-        <v>0.755085289478302</v>
+        <v>0.7154884934425354</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Welche Arten von Waffen werden aktuell an die Ukraine geliefert?
-Wie ist der Deal zwischen der Ukraine und Deutschland strukturiert?
-Sollte Deutschland weiterhin Waffen an die Ukraine liefern?
-Wer hatte diese Idee? Und was sind die Gedanken dahinter?
-Was genau ist Leihmutterschaft und warum ist sie in Deutschland verboten?
-Welche Risiken gehen mit der Leihmutterschaft einher?
-Was spricht für eine Aufhebung des Verbots? Was ist deine Meinung zu diesem Thema?</t>
+          <t>Deutschland liefert ja Waffen an die Ukraine. Auf der einen Seite finde ich das schlecht, da wir dadurch diesen Krieg unterstützen, aber auf der anderen Seite wollen wir den Leuten ja helfen. Ich bin jedoch jetzt nicht super informiert was das ganze Thema angeht, und das hängt natürlich auch alles stark von der Perspektive ab. Profitieren wir eigentlich von diesen Waffenlieferungen? Was sind moralische, aber auch wirtschaftliche und weltpolitische Argumente für und gegen die Waffenlieferungen? Bitte gebe mir auch ein paar unabhängige / objektive Quellen und Berichterstattungen zu dem ganzen Thema. In letzter Zeit wird ja immer wieder diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Auf der einen Seite halte ich das irgendwie für sinnvoll, aber irgendwie sträubt sich in mir auch etwas gegen solch eine Verpflichtung, vor allem wenn es um militärische Dinge geht. Kannst du mir helfen, mich genauer mit dieser Frage und den Pro- und Contra-Argumenten auseinander zu setzen, und was die genauen Rahmenbedingungen bei sowas wären? Bitte nenne mir auch einige Quellen dazu. Ich hab neulich eine Debatte über das erlauben der aktiven Sterbehilfe unter bestimmten Vorraussetzungen gehört. Da ich mich nicht so gut mit dem Thema auskenne wollte ich mal nachfragen, was denn gute Gründe dafür oder dagegen sind? Bitte gebe mir auch ein paar seriöse Quellen dazu.</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8262045383453369</v>
+        <v>0.7164098024368286</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8218370676040649</v>
+        <v>0.7519318461418152</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8395134806632996</v>
+        <v>0.7350844740867615</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8014184236526489</v>
+        <v>0.7406771183013916</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7471118569374084</v>
+        <v>0.7392157316207886</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wie sieht die aktuelle Situation im Ukraine Krieg aus? Wie hat sich die Situation im letzten Jahr verändert und wie viele und welche Waffen werden aktuell noch benötigt?
-Ist der impact der Deutschen Waffenlieferungen erkennbar? Können wir davon ausgehen das es bald zu einer waffenruhe oder einem ende des Konflikts kommt, wenn wir weiterhin die Ukraine unterstützen?
-Gibt es einen Messbaren oder belegbaren positiven Einfluss auf die Gesellschaft durch den sozialen/ Wehrdienst? Oder liegt nur ein Militärischer Wert vor?
-Ich gehe davon aus das die aktuell eher negative Situation der Bundeswehr eher von zu niedrigen Ausgaben aufgrund der starken Ersparnisse der letzten Jahrzehnte stammt. Kannst du das im Kontext der Fragen ob der Wehrdienst sinnvoll ist bestätigen oder wiederlegen?
-In welchen Ländern ist die Leihmutterschaft erlaubt und wie ist die resonanz darauf?
-Gibt es häufig Komplikationen durch die Leihmutterschaft?
-Wie geht es Kinder aus Leihmutterschaft? Kannst du dazu Daten und Fakten finden?</t>
+          <t>Waffenlieferung Deutschland an die Ukraine: Zeitraum Kriegsbeginn 2022 bis jetzt Juli 2026, inkludiere öffentlichen Diskurs Was sind die Vor- und Nachteile eines verpflichtenden Gesellschaftsdienstes für junge Menschen? Was sind die Vor- und Nachteile aktiver Sterbehilfe in Deutschland</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.861208975315094</v>
+        <v>0.7057021260261536</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8493391275405884</v>
+        <v>0.7283973097801208</v>
       </c>
       <c r="E8" t="n">
-        <v>0.871198296546936</v>
+        <v>0.7182833552360535</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8317373394966125</v>
+        <v>0.7206206321716309</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7817109823226929</v>
+        <v>0.6959307193756104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wie ist denn aktuell die Lage, um die nötigen Waffen an die Ukraine zu schicken. Könnten Sie mir die aktuelle Lage zuerst darlegen, bevor ich mich endgültig entscheide.
-Hat dieser Krieg weitere Folgen für uns?
-Können wir die Menschen anders unterstützen ohne wirklich Waffen an die Ukraine zu schicken?
-Ab welchem Alter ist der militärische Dienst denn verpflichtend?
-Wie lange soll der militärische Dienst denn gehen?
-Was hat das für wirtschaftliche und gesellschaftliche Folgen, wenn der militärische Dienst wieder in Kraft tritt?
-Gibt es Verträge, die den Schutz der Involvierten absichert?
-Unter welchen Umständen ist die Abtreibung des Kindes erlaubt?
-Gibt es Situationen, in denen die Krankenversicherung die Bezahlung einer Leihmutterschaft übernehmen kann?</t>
+          <t>Gib mir Argumente, warum Deutschland an die Ukraine Waffen und militärische Ausrüstung liefert, um sie gegen den russischen Angriffskrieg zu unterstützen. Seit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert. gib mir dazu Pro- und Contra-Argumente. Ich möchte mir meine eigene Meinung bilden, ob Deutschland Waffen an die Ukraine liefern sollte, um sie im Krieg gegen Russland zu unterstützen. Gub mir dazu eineige Fakten und Argumente für Pro- und Contra. In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden. Gib mir nähere Informationen, damit ich mir eine eigene Meinung bilden kann. Ich setze mich mit der Frage auseinander, wie ich zu einem verpflichtenden Gesellschaftsdienst in Deutschland stehe. Gib mir konkrete Fakten und Argument Pro und Contra. In Deutschland ist die aktive Sterbehilfe (Tötung auf Verlangen) verboten. Es wird jedoch immer wieder diskutiert, ob sie unter bestimmten Bedingungen legalisiert werden sollte — etwa bei unheilbaren Krankheiten und auf ausdrücklichen Wunsch der betroffenen Person. Gib mir nähere Informationen, damit ich mir eine eigene Meinung bilden kann. Ich bin mir nicht sicher, wie ich zu einer möglichen Legalisierung aktiver Sterbehilfe in Deutschland stehen soll. Worum geht es da genau und was sind Argumente von Gegnern und Befürwortern.</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8425754308700562</v>
+        <v>0.7329710125923157</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8158294558525085</v>
+        <v>0.7667218446731567</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8372302651405334</v>
+        <v>0.7493022084236145</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8107966184616089</v>
+        <v>0.7582950592041016</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7259004712104797</v>
+        <v>0.7302672863006592</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fasse die derzeitige Lage des Ukraine Kriegs zusammen. Welche Länder senden derzeit Waffen an die Ukraine und in welche Dimension?
-Welche Schritte werden derzeitig unternommen, um Verhandlungen über ein Ende des Krieges aufzunehmen? Was sind die Vorderungen an denen diese Verhandlungen momentan scheitern?
-Was sind die aktuellen rechtlichen Rahmenbedingungen bezüglich eines gesamtgesellschaftlichen Pflichtjahrs für junge Erwachsene in Deutschland?
-Gibt es Schätzungen über den Fachkräftemangel in sozialen Berufen in Deutschland? Könnte dieser durch ein soziales Pflichtjahr aufgefangen werden?
-Gibt es Studien zu den persönlichen Auswirkungen von Zivildienst und der Grundausbildung in Deutschland?
-Was ist die aktuelle rechtliche Lage zu Leihmutterschaften in Deutschland?
-Aus welche Gründen sind Leihmutterschaften gegebenenfalls notwendig? Welche Argumente sprechen gegen Leihmutterschaften?</t>
+          <t>„Welche Bedeutung hat die deutsche Geschichte (z. B. Zweiter Weltkrieg, Rolle als Zivilmacht) für die Debatte über Waffenlieferungen an die Ukraine?“ „Was sind die wichtigsten Argumente für und gegen einen verpflichtenden Gesellschaftsdienst für junge Menschen in Deutschland? Bitte neutral und übersichtlich darstellen.“ „Hilf mir dabei, mir eine eigene Position zu einem verpflichtenden Gesellschaftsdienst zu erarbeiten. Welche Fragen sollte ich mir selbst stellen (z. B. Freiheit, Gerechtigkeit, Nutzen für die Gesellschaft)?“ „Wie wird aktive Sterbehilfe ethisch und rechtlich bewertet (Menschenwürde, Selbstbestimmung, Schutz vulnerabler Personen)? Wo liegen die zentralen Konfliktpunkte?“</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8077369928359985</v>
+        <v>0.7572456002235413</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8039563894271851</v>
+        <v>0.7936955690383911</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8220474720001221</v>
+        <v>0.7686826586723328</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7766627669334412</v>
+        <v>0.7819925546646118</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6935233473777771</v>
+        <v>0.7577553391456604</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>62</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Welche Waffen liefert Deutschland an die Ukraine? Nenne mir die Gründe für verpflichtender Gesellschaftsdienst Kann der verpflichtender Gesellschaftsdienst für junge Menschen das Problem wirklich lösen? Wo ist aktive Sterbehilfe erlaubt? Vergleiche bzw. was hat dies für Auswirkungen?</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7323598861694336</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7697756290435791</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7445139288902283</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7556512951850891</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7312883138656616</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Liste Gründe auf, weshalb sich die deutsche Regierung dazu entschieden hat Waffen an die Ukraine zu liefern und benenne Vor- und Nachteile dieser Entscheidung. Wie würdest du nach Abwägung der genannten Vor- und Nachteile die Entscheidung der Regierung bewerten? Welche Argumente überwiegen? Nenne die Vor- und Nachteile eines verpflichtenden Gesellschaftsdiensts in Deutschland. Worauf sollte bei entsprechender Umsetzung geachtet werden? Was spricht für eine Legalisierung der aktiven Sterbehilfe in Deutschland? Liste Argumente auf und wäge sie mir den entsprechenden Gegenargumenten ab.</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.7071711421012878</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7593683004379272</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.7287708520889282</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.7457579374313354</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7160979509353638</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Seit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert. Warum sollte DE Waffen an die Ukraine liefern und warum nicjt. In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden. Welche Punkte sprechen für einen verpglichtende Gesellschaftsduenst in Deutschlabd und welche gegen? Welche Punkte sprechen für &amp; gegen die legalisierung aktiver sterbehilfe in deutsvhland Danke</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7400529384613037</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.764156699180603</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7472032308578491</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7564439177513123</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7311228513717651</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>65</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Verhalten Sie sich wie ein möglichst objektiver Wissenschaftler, der über die Vor und Nachteile der militärischen Unterstützung der Ukraine in Form von Waffenlieferungen aufklärt. Behandeln Sie dabei auch Thematiken, die über die viel öffentlich diskutierten Themen hinausgehen und Perspektiven, die meist im öffentlichen Diskurs ausgelassen werden. Versetzen Sie sich in die Lage einer Expertin für Gesellschaftsdienste, die BürgerInnen zu informieren versucht ohne jegliche Biases, es stehen keine anderen Interessen im Hintergrund. Welche Vor und welche Nachteile gibt es? Diskutieren Sie die Ethischen und Moralischen Für und Widersprüche für eine aktive Sterbehilfe in Deutschland. Agieren Sie hierbei als Empathischer Sozialwissenschaftler mit Ethik und Moral die explizit nicht aus religiösen Hintergründen stammt. Bitte beziehen Sie sich hierbei auch auf Daten und Fakten.</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7390579581260681</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7785705924034119</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.753381073474884</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7612545490264893</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7591039538383484</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>66</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Warum liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine und was wäre die Reaktion, wenn Deutschland die Lieferungen einstellen würde? Führe Pro- und Contra Argumente bezüglich der Einführung eines verpflichtenden Gesellschaftsdiensts für junge Menschen in Deutschland auf. Erkläre, warum die aktive Sterbehilfe in Deurschland noch nicht legalisiert wurde und nenne mögliche Faktoren, die sich ändern müssten.</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7214179635047913</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7552675008773804</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7282373309135437</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.7408340573310852</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7242125272750854</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>67</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wie hoch sind Deutschlands Ausgaben für Waffenlieferungen an die Ukraine jährlich? Haben die Waffenlieferungen Deutschland an die Ukraine positive Auswirkungen auf das Kriegsgeschehen? Nenne mir Beispiele, wie so ein verpflichtender Gesellschaftsdienst aussehen könnte. Wie realistisch ist es, das dieser Dienst in Zukunft eingeführt wird? Wie sieht die konkrete Gesetzeslage zur Sterbehilfe in Deutschland aus?</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6963861584663391</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.7258185148239136</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7128356695175171</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7150477766990662</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6975558400154114</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>68</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deutschland liefert aktuell einige Waffen an die Ukraine. Ich befürworte dies allgemein und frage mich zudem, weshalb diese Waffenlieferungen nicht in einem Umfang geschehen, der der Ukraine tatsächlich ermöglicht militärisch erfolgreich zu sein. Kannst du eine präzise Analyse verfassen, warum dies aktuell nicht geschieht und was die Rationale dagegen und dafür sind? Aktuell wird in Deutschland über ein verpflichtendes Dienstjahr diskutiert. Da ich selbst nicht mehr davon betroffen bin, hinterfrage ich meine befürwortende Position. Was würde gegen ein solches Dienstjahr sprechen? Ich beschäftige mich aktuell mit dem Thema, ob die aktive (ärztlich durchgeführte) Sterbehilfe in Deutschland legalisiert werden sollte. In verschiedenen Diskussionen und im klinischen Alltag hatte ich bereits etwas Kontakt zu dem Thema, allerdings fehlt mir insbesondere der ethische Bezug. Bitte stelle mir hierzu eine durchdachte Diskussion verschiedener Argument zusammen, die mir helfen das Thema für mich zu beantworten.</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7148746848106384</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.752351701259613</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7337033748626709</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.74123215675354</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7268995642662048</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>69</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hallo ChatGPT was sind pro und kontraargumente für eine deutsche Waffenlieferung in die Ukraine? wie positionieren sich die Parteien Deutschlands zur deutschen Waffenlieferung in die Ukraine? Warum wird die deutsche Waffenlieferung in die Ukraine neu diskutiert Was sind Gründe für und gegen einen Gesellschaftsdienst für junge Menschen? Welche Regeln soll der Gesellschaftsdienst haben? Was fällt darunter? In welchen Ländern wird aktive Sterbehilfe wie durchgeführt?</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6808134317398071</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7083884477615356</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6954663395881653</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6971866488456726</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6815680265426636</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>70</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>meinung Deutschlandl liefert  Waffen an die Ukraine verpflichtenden Gesellschaftsdienst in Deutschland Legalisierung aktiver Sterbehilfe in Deutschland</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6792608499526978</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.7119913697242737</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6966075301170349</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7079423666000366</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6541974544525146</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>74</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wie viel waffen (für wie viel geld) liefert deutschland an die ukraine? gebe mir eine pro/kontra liste für waffenlieferungen an die ukraine was wäre der kosten nutzen vergleich wenn man ein gesellschaftsdienst für alle nach dem abschluss einführen würde &amp; jeder so 500/600 euro i monat verdienen würde was sind pro argumente vorallem in der hinsicht darauf, was zb das gesundheitssystem "einsparen" könnte?</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6934792399406433</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.7305330038070679</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7125522494316101</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7159128785133362</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7049503326416016</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>75</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Seit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert. Nenne mir Pro und Contra Argumente. In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden. Bitte nenne mir Pro und Contra Argumente. In Deutschland ist die aktive Sterbehilfe (Tötung auf Verlangen) verboten. Es wird jedoch immer wieder diskutiert, ob sie unter bestimmten Bedingungen legalisiert werden sollte — etwa bei unheilbaren Krankheiten und auf ausdrücklichen Wunsch der betroffenen Person. Nenne mir Pro und Contra Argumente.</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7657024264335632</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.7973504066467285</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7743698358535767</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7879126667976379</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7580825686454773</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>78</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Wie viele und welche Waffen liefert Deutschland in die Ukraine? Hat der Waffentransport negative Auswirkungen auf die deutsche Wirtschaft und Sicherheit? Was bringt der verpflichtende Gesellschaftsdienst und ab wie vielen Jahren soll er eingeführt werden? Wie ist die aktuelle Rechtslage in Deutschland bezüglich der aktiven Sterbehilfe? Welche Länder bieten die aktive Sterbehilfe an und wie ist dort die Rechtslage? Nenne mir Pros und Cons bezüglich der aktiven Sterbehilfe.</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.6817205548286438</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.7164410948753357</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.699242115020752</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7039802074432373</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.6924405097961426</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>80</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nenne mir Fakten über die Waffenlieferungen Deutschlands an die Ukraine. Mich interessiert besonders, wie es der Ukraine ohne diese Waffen gehen würde, welche Auswirkungen es auf unsere Beziehungen zu Russland haben könnte, wenn wir keine Waffen mehr liefern würden und wie groß der Umfang der Waffenlieferung ist (materiell, aber auch, was es kostet). Nenne mir Vor- und Nachteile für einen verpflichtenden Gesellschaftsdienst für junge Menschen in Deutschland. Zeige mir Vorschläge und Gegenargumente bezüglich der Einführung der aktiven Sterbehilfe in Deutschland. Gehe auch auf Beispiele aus Nachbarländern ein (zum Beispiel Schweiz).</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7124379873275757</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.7383991479873657</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.7272779941558838</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.7271773815155029</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.7130137085914612</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>83</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Für was werden die Waffen benutzt, die Deutschland an die Ukraine liefert? Wie viel Geld gibt Deutschland aus, um Waffen in die Ukraine zu liefern? Welche Aufgaben / Arbeit könnte ein verpflichtender gesellschaftsdienst beinhalten? Was könnte passieren, wenn es einen verpflichtenden Dienst gibt und man diesen verweigert? Weshalb ist die Sterbehilfe momentan in Deutschland verboten? Was spricht gegen das Verbot einer Sterbehilfe? In welchen Ländern ist die Sterbehilfe legalisiert und welche Kriterien wurden angeführt für die Legalisierung?</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.7131803631782532</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.7506293654441833</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7240830063819885</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.7368133068084717</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.7118005156517029</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>84</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Was spricht jeweils dafür und dagegen, dass Deutschland weiterhin Waffen an die Ukraine liefert? Welche Meinungen gibt es dazu und gibt es Tendenz, wie einzelne Bevölkerungsgruppen (z.B. nach Alter, sozialer Schicht o.ä.) dazu stehen? Was kann ich mir genau unter einem verpflichtenden Gesellschaftsdienst für junge Leute in Deutschland vorstellen? Wie viel Mitspracherecht hätten die Betroffenen da? Was wären die Rahmenbedingungen wie Dauer, Lohn, Möglichkeiten etc.? Wie sieht das aktuelle Stimmungsvild diesbezüglich in Deutschland aus, gerade auch aus unterschiedlichen Altersgruppen (potentiell Betroffene vs. Nicht-Betroffene)? Welche Auswirkungen werden sich daraus versprochen? Welche Argumente für und gegen aktive Sterbehilfe werden in Deutschland diskutiert? Welche Alternativen gibt es oder könnten angeboten werden? Einige Menschen, die in Deutschland keine aktive Sterbehilfe erhalten, gehen dafür ja ins Ausland. Machen sich Menschen, die dabei helfen, derzeit auch strafbar? Wenn beispielsweise jemand so schwer krank, verletzt oder behindet ist, dass er/sie die Reise etc. gar nicht selbst organisieren könnte oder schlicht das Geld dafür nicht hat, dürfen andere Menschen (Deutsche) da helfen?</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7505664825439453</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7834440469741821</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.764095664024353</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.7654131054878235</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.7676377296447754</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>86</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>In welchem Umfang liefert Deutschland Waffen an die Ukraine? Welchen Anteil der gelieferten Waffen macht das aus? Welche Punkte sprechen für oder gegen ein verpflichtende FSJ? Wie sind die aktuellen Rahmenbedingungen zur aktiven sterbehilfe? Wie ist das Thema in unseren Nachbarländer geregelt? Welche Punkte sprechen für oder gegen die Legalisierung der aktiven sterbehilfe?</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7233929038047791</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.756009042263031</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7386432290077209</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.7446581721305847</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.7256006598472595</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>87</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Warum liefert Deutschland Waffen an die Ukraine Was spricht gegen Deutschlands militärische Unterstützung zur Ukraine Welche jetzige politische Situation fördert die Regierung einen verpflichtenden Gesellschaftsdienst durchzusetzen Wen würde ein verpflichtender Gesellschaftsdienst betreffen und was sind die Ausnahmen dazu Welcher Politiker/Herrscher hat den Verbot von der Sterbehilfe erschaffen Wie könnte eine aktive Sterbehilfe der Gesellschaft helfen/schaden</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7658232450485229</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.8034446835517883</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7774286866188049</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7922385334968567</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.7607771158218384</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>88</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Was sind Gründe dafür und dagegen, dass Deutschland Waffen in die Ukraine importiert? Warum will man den Zivildienst wieder einführen? Warum ist Sterbehilfe in Deutschland verboten?</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.6997849345207214</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.7250705361366272</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6991857290267944</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.7118744850158691</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.6981048583984375</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>90</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Wie sinnvoll ist es dass wir waffen in die Ukraine liefern Könnte uns Russland deswegen angreifen ? Warum verpflichtenden Sozialdienst als Jugendlicher machen ? Warum gibt es in Deutschland keine Sterbehilfe ?</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7116889357566833</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7353070974349976</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7139319181442261</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.7222916483879089</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.7061843276023865</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>92</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Schreibe eine pro und Kontra Liste mit Argumenten zu dem Thema ob Deutschland weiter waffen an die Ukraine liefern sollte. Erkläre den Hintergrund des Krieges und was genau  Deutschlands Rolle hierbei ist. Was sind die Vorteile von dem einführen von einem Gesellschaftsdienst für junge Menschen in Deutschland. Was sind Probleme bei dem verpflichtenden gesellschaftsdienst für junge Menschen? Was sind Argumente dafür sterbehilfe allgemein bzw. In Deutschland zu legalisieren? Was sind Gegenargumente dafür sterbehilfe zu legalisieren? Gib Beispiele von den Auswirkungen wo sterbehikfe bereits legalisiert worden ist.</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6931070685386658</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7265738844871521</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7112182378768921</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.7168844938278198</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.6943709254264832</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>93</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Wie viele Waffen und in welchem Wert hat Deutschland bisher an die Ukraine geliefert? Woher nimmt Deutschland das Geld? Das ist ja nicht direkt unser Krieg und hier im Land gibt es riesige Baustellen, die auch Geld bräuchten Gibt es irgendeinen Endpunkt oder wird unendlich Geld und Waffen zur Verfügung gestellt, solange der Krieg eben läuft? Wie genau sieht der aktuell diskutierte verpflichtende Gesellschaftsdienst für junge Menschen aus? Welchen Zeitraum würde das umfassen und kann man so wie bei FSJ und BFD seine Einsatzstelle selbst wählen? Wurde nicht 2020 das entsprechende Gesetz (Verbot von aktiver Sterbehilfe) für verfassungswidrig erklärt, da zu einem selbstbestimmten Leben auch selbstbestimmtes Sterben gehört? Bei einer Legalisierung - welche Hürden gibt es dennoch? Wie niedrigschwellig sind die Angebote? Welche Mittel gäbe es? Kann frei gewählt werden?</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7474029064178467</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.778659462928772</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7561737298965454</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.7628647089004517</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.754578709602356</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>94</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ist Waffenlieferung Kriegsbeteiligung? Wie viele deutsche Waffen bisher in Ukraine? Was sind Vorteile von Gesellschaftsdienst? Sterbehilfe Kritikpunkte Wo Sterbehilfe legal?</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7436651587486267</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.7749453186988831</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7440119981765747</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.7629882097244263</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.7178061604499817</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>95</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>warum beliefern wir die ukraine mit waffen? fördern wir damit nicht den Krieg? sollten wir nicht eher nach einem weg zum waffenstillstand suchen?
+bitte informiere mich umfassend damit ich mir dazu meine eigene meinung bilden kann ein verpflichtender gesellschaftsdienst wird ja momentan heiß diskutiert. Kannst du mir bitte die vor und nachteile umfassend zeigen, damit ich meine eigene meinung dazu im idealfall verstärken kann? In DE ist ja die aktive Sterbehilfe verboten, in anderen Ländern aber nicht. Was sind die Argumente warum es bei uns verboten ist aber in Belgien zum beispiel nicht. dann gibt es ja auch noch den assistierten Suizid.
+Grundsätzlich bin ich eher dafür aber kann mir auch vorstellen das man so ein Gesetz auch stark missbrauchen kann. Bitte gib mir ausführliche informationen dazu.</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7211174368858337</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.7576461434364319</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7360245585441589</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.7440329790115356</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.7349984049797058</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>96</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>erkläre mir den Ukrainekonflikt und Gründe warum Deutschland Waffen an die Ukraine liefert nenne mir pro und kontras zum verpflichtenden Gesellschaftsdienst und vergleiche es mit anderen Systemen in versch. Ländern welche Meinungen gibt es zur aktiven Sterbehilfe und wie werden sie begründet</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.675749659538269</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.7130550146102905</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6934259533882141</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.696631133556366</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.6742811799049377</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>97</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hallo KI, Ich mag mich gerne mit deutschen Waffenlieferungen an die Ukraine auseinandersetzen. Dass Deutschland Waffen liefert wird ja von verschiedenen Seiten in der deutschen Öffentlichkeit diskutiert. Kannst du mir erstmal eine kurze Zusammenfassung der Positionen der Parteien im Bundestag liefern? Aber wirklich kurz. Kannst du auch noch andere wichtige Akteure in der Öffentlichkeit einbeziehen (sowas wie Gewerkschaften, Arbeitgeber, NGOs... wen du für wichtig hältst). Danke für die Zusammenfassung! Kannst du auch darstellen, wie sich die öffentliche Meinung geändert hat seit dem Beginn des Kriegs in der Ukraine? Und dann würde mich noch interessieren wie die öffentliche Meinung und Diskussion in anderen europäischen und Nato-Ländern aussieht. Besonders in Nachbarländern der Ukraine oder Russlands und dann auch noch in Ländern wie den USA die eher weit weg liegen. Hallo, der Hintergrund ist folgender: "In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden."
+Kannst du mir zuerst kurz auflisten, welche Gruppierungen/ Parteien etc das ins Gespräch gebracht haben, mit welcher Begründung, und welche Positionen dazu vertreten werden von Parteien, NGOs, Gewerkschaften, jungen Menschen die betroffen wären...
+Ich bin interessiert an einer Erörterung von pro und kontra eines solchen Gesellschaftsdienstes um mir eine eigene Meinung zu bilden. Gibt es sowas schon in anderen Ländern? Was sind die Erfahrungen dort? Gibt es Ideen, ob und wie junge Menschen dafür entlohnt werden würden? Hallo liebe KI, in Deutschland ist ja die aktive Sterbehilfe verboten. Es gibt Diskussionen, ob sie unter bestimmten Bedingungen legalisiert werden sollte (z.B. bei unheilbaren Krankheiten oder auf ausdrücklichen Wunsch der betroffenen Person). Dazu mag ich mir gern eine differenziertere Meinung bilden und das ganze aus verschiedenen Blickwinkeln betrachten.
+Was sind die Positionen von Ärzteverbänden, Parteien, etc. Welche Gruppen wären hier überhaupt wichtig anzuhören?
+Gibt es aktive Sterbehilfe in anderen Ländern, was sind die Erfahrungen dort? Meine Schwiegermutter ist Ärztin und sagt häufiger "Man soll nie einem Patient die Hoffnung nehmen". Wie würde man das mit Sterbehilfe in Einklang bringen? Wie würde bzw. könnte man entscheiden, wer aktive Sterbehilfe in Anspruch nehmen kann? Welche rechtlichen Rahmenbedingungen müsste man in Deutschland schaffen, damit das für "sterbehelfende" Ärzte rechtssicher wäre. Sie sollen ja bei einer möglichen Legalisierung sicher sein können, nicht etwa von Angehörigen belangt zu werden.</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7432290315628052</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.7801133394241333</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7638686895370483</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.7676119804382324</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.7573423981666565</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>98</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Was für Auswirkungen würde eine Waffenlieferung von Deutschland an die Ukraine aktuell bedeuten und welche Systeme würden geliefert werden? Wie sah der alternativdienst zur Wehrpflicht in Deutschland aus? Was gibt es gerade für freiwilligen Dienste (z.B. FSJ)? Wo gibt es bereits Sterbehilfe und gibt es Studien dazu wie es genutzt wird bzw. was die Bevölkerung in diesen Ländern sagt?</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6958660483360291</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.7203606963157654</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7119979858398438</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.7093779444694519</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.6886565089225769</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>99</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Wie viele und welche Art von Waffen liefert Deutschland an die Ukraine? Wie hilfreich sind die im Kampf gegen Russland? Hat die Ukraine durch deutsche Waffenlieferungen eine höhehere Überlebenschance? Welchen Bedarf kann Deutschland decken, um effektiver zu helfen ohne selbst große Lücken zu hinterlassen? Worüber ist die Debatte des verpflichtenden Gesellschaftsdienstes in Deutschland gerade? Ist sterbehilfe in Deutschland legal? Wie genau funktioniert die und wie sicher ist die?</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6614909172058105</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.6925472617149353</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6745173335075378</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.6801366806030273</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.6725882887840271</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>101</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>welchen umfang haben waffenlieferungen von deutschland in die ukraine, im verhältnis zu deutschen ausgaben generell, aber auch im europäischen vergleich. was könnte man alternativ mit dieser summe machen, was sind kritische probleme in deutschland die angegegangen werden müssten die dadurch nennenswert profitieren wprden. gibt es informationen dazu ob die waffenlieferungen in der ukraine sinnvoll eingesetzt werden können was denkst du darüber ob weiter waffen geliefert werden sollen recherchiere zum möglichen verplichtenden Gesellschaftsdienst in deutschland und spezifiziere diesen genauer, wie soll er ausgestaltet werden, bspw. mit welchem alter, wie lange, kann man sich die tätigkeitsstelle aussuche, wird zugewiesen, wie wird er vergütet lege dar welche aspekte für und gegen einen solchen gesellschaftsdienst sprechen wie ist die aktuelle situation zur aktiven sterbe hilfe in deutschland? wie ist es in anderen ländern geregelt was ist der konkrete vorschlag wie aktive sterbehilfe in deutschland legalisiert werden soll welche aspekte sprechen für und gegen diese initiative</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7293383479118347</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.7666518688201904</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7448680996894836</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.7514855265617371</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.7356200218200684</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>102</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sollte Deutschland weiterhin Waffen an die Ukraine liefern? Ist es eine gute Idee, wenn Deutschland weiterhin Waffen an die Ukraine liefert? Sollten alle jungen Leute nach der Schule dazu verpflichtet sein, einen Freiwilligen Dienst auszuführen oder besser nicht? Sollte aktive Sterbehilfe in Deutschland legalisiert werden oder nicht?</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7244858741760254</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.7483801245689392</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7340867519378662</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.7383032441139221</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.7241889834403992</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>103</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pro und Contra Waffenlieferungen an die Ukraine? Pro und Contra Waffenlieferungen? Wie viel Geld fließt in Waffenlieferung an die Ukraine in Deutschland? Wie würde ein verpflichtender Gesellschaftsdienst in Deutschland aussehen? Pro und Contra verpflichtender Gesellschaftsdienst? Wie wahrscheinlich ist ein verpflichtender Gesellschaftsdienst in Deutschland? Was sind pros und cons zur Sterbehilfe? Welche Gesetze verbieten Sterbehilfe in Deutschland? Welche moralischen Werte sind wichtig für Sterbehilfe?</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6542122960090637</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.6971181035041809</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6764086484909058</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.685455858707428</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6551133394241333</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>106</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nenne mir Pro und Contra Argumente einer Lieferung von Waffen und militärischer Ausrüstung an die Ukraine. Was wären mögliche Konsequenzen einer vermehrten oder reduzierten Lieferung? Nenne mir Pro und Contra Argumente eines verpflichtenden Gesellschaftsdienst für junge Menschen, welcher soziale, ökologische oder militärische Aufgaben umfassen kann. Erläutere mir, wie eine Umsetzung realistisch funktionieren könnte. Was sind die Standpunkte der Grünen, CDU, SPD und Linken? Nenne mit Pro und Contra Argumente einer Legalisierung der aktiven Sterbehilfe (Tötung auf Verlangen). Wie könnte eine Umsetzung der Legalisierung realistisch aussehen?</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7639272809028625</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.8044697046279907</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.783902108669281</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.7929989695549011</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.761131227016449</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>109</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Wieso beliefert deutschland die Ukraine mit waffen ? Kann es zu einem Problem werden das Deutschland die Ukraine mit Waffen versorgt? Was ist die meinung der Deutschen Gesellschaft dazu ? Sollte man in deutschland ein Verpflichtetend Gesellschaftsdiensz einführen? Was könnte dafür und was dagegen sprechen ? Was Spricht für und gegen eine Legalisierung der aktiven Sterbehilfe?</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6976556777954102</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.7267613410949707</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7143036127090454</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.7146859765052795</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.6979849934577942</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>111</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Warum liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine? Was sind politische Beweggründe? Welche Punkte sprechen dafür oder dagegen? Schützt dies unsere Demokratie? Stelle die aktuelle Lage der DIskussion und der Argumente für oder gegen einen Gesellschaftsdienst in einer Tabelle dar. Erstelle eine klare, objektive pro/contra Liste mit Argumenten für und gegen aktive Sterbehilfe.  Was könnten negative/positive Folgen einer Legalisierung der Sterbehilfe in Deutschland sein?</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7426633238792419</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.778838038444519</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7576372027397156</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.7678784728050232</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.746099591255188</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>114</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Welche Argumente gibt es für und gegen die Waffenlieferung Deutschlands an die Ukraine in bezug auf den russischen Angriffskrieg? Nimm selbst keine position ein, sondern schildere sachlich unterschiedliche Argumente Welche Argmente gibt es für und/oder gegen einen verpflichtenden Gesellschaftdienst (Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen) für junge menschen in Deutschland? Nimm selbst keine Position ein sondern schildere sachlich Argumente für beide Seiten Welche Argmente gibt es für und/oder gegen eine aktive Sterbehilfe in Deutschland? Nimm selbst keine Position ein sondern schildere sachlich Argumente für beide Seiten</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.7295550107955933</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.7723254561424255</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.7477833032608032</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.7586321234703064</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.7394465804100037</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>115</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Wie würde eine Welt aussehen in der Deutschland Waffen an die Ukraine liefert? Was bedeutend Waffenlieferungen für mich als Privatperson? Was wären die Vor und Nachteile eines Gesellschaftsdienst nach der Schule? Nimmt ein Gesellschaftsdienst nach der Schule positive Effekte auf unsere Gesellschaft? Wie läuft eine aktive Sterbehilfe ab? Was sind die ethischen Nachteile einer aktiven Sterbehilfe?</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.6993542909622192</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.7314819693565369</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.7184235453605652</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.7189958095550537</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.7159785032272339</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>116</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Wie findest du es, dass Deutschland Waffen an die Ukraine liefert? Ich bin noch unentschlossen. Nenne mir Vor- und Nachteile der Waffenlieferung Deutschlands an die Ukraine. Welche Vor- und Nachteile gibt es in Bezug auf einen verpflichtenden Gesellschaftsdienst für junge Menschen? Nenne mir Vor- und Nachteile der aktiven Sterbehilfe (in Deutschland).</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.6504713296890259</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.6790276765823364</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6667923927307129</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.6668093204498291</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.6536827087402344</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Was würde passieren, wenn deutschland aufhören würde Waffen zu liefern? Würde die Ukraine sofort den Krieg verlieren? Warum ist es wichtig das Deutschland Waffen liefert? Wer ist alle bestroffen wenn es einen verpflichteten Gesellschaftsdienst gibt und was müsste man dann machen? Wenn es legal wäre, gibt es schon konkrete Pläne wie das ablaufen würde. Also wie schwer/leicht es sein wird und welche Vorraussetzungen hat das?</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.6981354951858521</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.7265042662620544</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.6972058415412903</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.7095302939414978</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.7115392684936523</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Gehört Ukraine zur EU und deswegen unterstützt DE die Ukraine? Wie ist das Verhältnis zwischen DE &amp; Russland? Flüchten immer noch Menschen aus der Ukraine nach DE? Was ist genau mit Gesellschaftsdienst gemeint? Sollen Jungen &amp; Mädchen involviert sein? Was genau bringt ein solcher Gesellschaftsdienst? Warum ist die Sterbehilfe in DE verboten? In welchen Ländern ist sie erlaubt?</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.6501328349113464</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.6799824237823486</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6616044640541077</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.6626126766204834</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.6623340249061584</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nachteile, wenn Deutschland keine Waffen mehr liefert Für wie lange soll der verpflichtende Gesellschaftsdienst geleistet werden Darf man sich aus dem militärischen Angebot entziehen? Was sind Vor und Nachteile der Sterbehilfe Warum sind manche dagegen Wie läuft das in anderen Ländern zb Schweiz ab</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7183210849761963</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.7572673559188843</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.7293703556060791</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.7362516522407532</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.73117595911026</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Welche Folgen hätte ein Stopp der Waffenlieferungen an die Ukraine? Welche Vor und Nachteile ergeben sich aus einem verpflichtenden Gesellschaftsdienst für junge Menschen? Was spricht für und was gegen die Legalisierung aktiver Sterbehilfe?</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7133214473724365</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7431755661964417</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7166854739189148</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.7301689386367798</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.7091302275657654</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Was sind Argumente für und gegen die deutschen Waffenlieferungen an die Ukraine? Gib mir bitte jeweils mehrere Argumente mit Quellen an. Ist ein verpflichtender Gesellschaftsdienst für junge Menschen sinnvoll? Wie wurde dies in der Vergangenheit behandelt und was waren die Ergebnisse von früheren verpflichtenden Diensten? Was sind Gründe, die für eine aktive Sterbehilfe angeführt werden? Warum sollte diese legalisiert werden oder illegal bleiben?</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.725012481212616</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.7575697898864746</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.7411859035491943</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.7469280958175659</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.7217934727668762</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Seit Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine (Beginn des russischen Angriffskriegs). Unabhängig von der deutschen Meinung: Bedenke alle Aspekte des Krieges. Besonders in Bezug auf Zukunft, geopolitische Situation, Europas Rolle, NATOs Rolle etc -&gt; Sollte Deutschland weiterhin Waffen und Ausrüstung an die Ukraine liefern? WIe viele Waffen etc hat Deutschland im Vergleich zu anderen PArtnern der Ukraine an die Ukraine geliefert? Ist das verhältnismäßig zu viel oder zu wenig? Liste mir selbst Punkte auf, die man in Bezug auf diesen Krieg noch weiterhin bedenken sollte. Stell dir vor du möchtest dich jetzt mit dieser Frage auseinandersetzen in einer Talkshow oder einem Youtube-Podcasts und faktenbasiert argumentieren können (unabhängig davon, ob Deutschland weiterhin liefern sollte etc oder nicht), was würdest du beachten. Stelle mir ein Handout zusammen mit allen wichtigen Infos Welche Vorteile hat ein Gesellschaftsdienst für junge Menschen und welche Vorteile für die Gesellschaft? Besonders die Aufgaben wie "ökologische, soziale oder militärische". Liste mir auch die Nachteile auf. Stell dir vor du bist ein junger Mensch und musst nach dem Schulabschluss einen verpflichtenden Gesellschaftsdienst leisten. Fändest du es gut oder schlecht und begründe wieso. Stell dir vor du bist jetzt etwas älter geworden und ein Bürger in Deutschland. Wie stehst du mittlerweile zum verpflichtenden Gesellschaftsdienstes. Was ist negativ an einer Legalisierung aktiver Sterbehilfe? Liste mir alle negativen Punkte auf. Überwiegen die negativen Punkte die positiven Punkte? Was hat sich in Ländern geändert, seitdem es die aktive Sterbehilfe gibt? Wie steht dort die Gesellschaft mittlerweile zu dem Thema. Ich glaube in den Niederlanden ist es legal und es gibt Hospize dafür?</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7145300507545471</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.7474772930145264</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7376061677932739</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.7372509837150574</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.7270550131797791</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ich möchte Informationen zu Waffenlieferungen die seit Februar 2022 in die Ukraine geliefert werden. Wie ist das Gesamtvolumen und wie teilt es sich auf alle beteiligten Länder, insbesondere Deutschland auf? Wie haben haben sich die Waffenlieferungen seit 2022 entwickelt? Welche Waffen werden geliefert?
+Erstelle einen Berichtder die obigen Fragen im Detail beantwortet und ordne die Fakten ein. Welche Argumente gibt es für und gegen Waffenlieferungen an ein drittes Land im Speziellen der Ukraine seit 2022? Gibt es Erhebungen zur Zahl Jugendlicher die einen verpflichtenden Gesellschaftsdienst befürworten? Welche Möglichkeiten gibt es in Deutschland einen Freiwilligendienst zu machen? Belege mit Quellen: wie viele Jugendliche haben Schwierigkeiten nach dem Schulabschluss den nächsten Schritt für sich zu finden? Wie viele Jugendliche sind sich sicher was sie nach dem Abschluss machen wollen? Gibt es Unterschiede je nach Bildungsgrad? Welche Argumente gibt es für und gegen aktive Sterbehilfe? Wie ist die Gesetzesgebung bezüglich Sterbehilfe in Ländern wo es erlaubt ist?
+Gibt es  Statistiken wie viele Personen pro Jahr Sterbehilfe in Anspruch nehmen?</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7165324687957764</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.7505394220352173</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.7324526906013489</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.7381429672241211</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.7218535542488098</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>133</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Gib mir einen Überblick über die aktuelle Situation in der Ukraine. Fokussiere dich dabei auch auf aktuelle Friedensbestrebungen Finde aktuellen Statistiken zu Deutschen Waffenlieferungen Finde Statistiken zu aktuellem Fachkräftemangel in Aufgabenfeldern die für ein verpflichtendes Gesellschaftsjahr in Deutschland in Frage kommen Suche und beschreibe die aktuelle rechtliche Situation zur aktiven Sterbehilfe in Deutschland. Beschreibe die rechtliche Situation in Ländern in denen aktive Sterbehilfe zugelassen ist. Gib mir 3 Pro und 3 Contra Argumente zur aktiven Sterbehilfe</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6900011301040649</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.7252534627914429</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.7146241068840027</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.7186115980148315</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.6952868700027466</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Was spricht dafür und dagegen, dass Deutschland Waffen an die Ukraine liefert? Was ist der Unterschied zwischen einem Gesellschaftsdienst und einem FSJ/BFD? Nenne Argumente pro und contra für einen verpflichtenden Gesellschaftsdienst Was spricht für und gegen aktive Sterbehilfe? ehtische/moralische Gründe</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.695910632610321</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.737348735332489</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7164159417152405</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.7282953262329102</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.7037358283996582</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Was kannst du mir über Waffenlieferungen Deutschlands an die Ukraine im zusammenhang mit der militärischen Auseinandersetzung mit Russland seit Februar 2022 sagen. Bitte belege deine Aussagen Anhand von Quellen angaben. Was kannst du mir über Waffenlieferungen Deutschlands an die Ukraine im zusammenhang mit der militärischen Auseinandersetzung mit Russland seit Februar 2022 sagen. Bitte belege deine Aussagen Anhand von Quellen angaben.
+Zusatz: Solltest du Informationen nicht belegen können, bzw sie sind schlussfolgerungen deinerseits, kennzeichne dies bitte. Was sind pro und Contra Argumente für einen verpflichtenden Gesellschaftsdienst für junge Menschen. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden. Eigentlich würde ich solche Thematiken nicht mit einer KI behandeln. Was sind wichitge Punkte und Argumente, welche in der Debatte um die aktive Sterbehilfe genannt werden. Bitte suche mir auch wichtige Beiträge welche sich mit dem Thema befassen heraus. Diese sollten bestenfalls beide Standpunkt umfassen.</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.7803943157196045</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.8100153207778931</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.7936931848526001</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.8001670837402344</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.7754154801368713</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Erstelle einer Übersicht der dominanten Positionen, Fakten und Meinungen zu dem Thema ob Deutschland weiterhin Waffen an die Ukraine liefern sollte, kennzeichne deine Quellen, und erläutere welche Mittel du eingesetzt hast um in deiner Recherche alle relevanten Themen miteinzubeziehen. Erstelle einer Übersicht der dominanten Positionen, Fakten und Meinungen zu dem Thema ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden sollte, kennzeichne deine Quellen, und erläutere welche Mittel du eingesetzt hast um in deiner Recherche alle relevanten Themen miteinzubeziehen. Erstelle eine Übersicht der prominentesten Positionen zur aktiven Sterbehilfe, zeichne Quellen auf die genutzt wurden und hinterfrage aktiv ob das Thema weitgreifend abgedeckt wurde</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.7558971047401428</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.7925887703895569</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.7793615460395813</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.7828990817070007</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.7707656621932983</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>138</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Warum hat Deutschland Waffen an die Ukranine geliefert und was waren die Folgen? Was sind Argumente für und gegen einen verpflichtenden Gesellschaftsdienst? Warum soll ein verpflichtender Gesellschaftsdienst eingeführt werden? Ist in anderen Ländern aktive Sterbehilfe erlaubt und ist dadurch die Anzahl an Sterbehilfefällen gestiegen? Welche Voraussetzungen müssten Patienten für die aktive Sterbehilfe erfüllen?</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.7167249321937561</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.7526232004165649</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7255962491035461</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.7375737428665161</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.7131708860397339</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>139</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Wie unterstützt Deutschland aktuell die Ukraine im Krieg? Welche Folgen hätte ein möglicher Stopp der Waffenlieferung? Wie könnte ein verpflichtender Gesellschaftsdienst aussehen und welche Vorteile hätte dieser? Wie viel Gehalt würde man bekommen? Was sind Argumente die dagegen sprechen? Wie sieht aktive Sterbehilfe aus? Wie regeln das andere Länder? Welche Regelung gibt es bei psychischen Krankheiten?</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7521905303001404</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.792242169380188</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7606080174446106</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.7725909352302551</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.7636183500289917</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>142</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Nenne mir bitte Argumente für und gegen die Waffenlieferung Deutschlands an die Ukraine. Erkläre mir was mit einem vepflichtenden Gesellschaftsdienst für junge Menschen gemeint ist bitte. Welche Positionen gibt es zu diesem Thema? Fasse mir bitte alle wichtigen Informationen zum Thema STerbehilfe zusammen und gib dabei stets die Quellen an. Wieso ist Sterbehilfe so kontrovers? Bitte erstelle mir eine Übersicht von verschiedenen ethischen Standpunkten.</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.7208067774772644</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.7550941705703735</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.743776261806488</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.7472756505012512</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.7226724028587341</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>143</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Welche Vorteile und Nachteile gibt es, wenn Deutschland weiterhin Waffen an die Ukraine liefert? Bitte nehme Bezug zum Ukrainekrieg der ketzten Jahre und den Weltgeschehnissen, bzw Verhältnissen zwischen dem Krieg und anderen großen Weltnationen. In Deutschland wird ein Gesellschaftsdienst diskutiert, der in verschiedenen Bereich ausgeübt werden kann. Nenne mir Vorteile und Nachteile Nenne mir Vor- und Nachteile einer rechtlich erlaubten Sterbehilfe in Deutschland. Welche weiteren Perspektiven ergeben sich dadurch? Haben Menschen kurz vor dem Ableben andere Alternativen?</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.7188195586204529</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.7529613971710205</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7259292602539062</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.7341557145118713</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.7253835201263428</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>152</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Welche begründungen/argumente werden genannt für oder gegen eine Waffenlieferung an die Ukraine und wer positioniert sich hier wie dazu? Wohin hat Deutschland schon alles Waffen geliefert, wie viel Waffen liefert Deutschland an die Ukraine?(wie viel evtl andere Länder und welche?) Was würde mit den Waffen passieren wenn Deutschland sie nicht an die Ukraine liefern würde? Kann die Ukraine sich länger verteidigen durch deutsche Waffenlieferungen? gibt es Studien dazu was ein verpflichtender gesellschaftlicher Dienst (FSJ etc) für Folgen hätte (gesellschaftlich sowie individiuell)? welche argumente werden dafür/dagegen genannt? wie weit ist der stand der diskussion bzgl eines verpflichtenden gesellschaftlichen dienstes, wo befindet sich die politik hier gerade? Wie realistisch ist eine Umsetzung bzw wie hoch die Wahrscheinlichkeit dass eine solche Pflicht eingeführt wird? welche diskussionspunkte gibt es bzgl aktiver sterbehilfe, welche pro/contra argumente werden häufig genannt? wo ist aktive sterbehilfe legal und wie lauten dort die begründungen für die legalisierung, welche begründungen gibt es in deutschland dafür dass aktive sterbehilfe illegal ist? gibt es studien dazu welche folgen eine legalisierung aktiver sterbehilfe hätte/in ländern in denen es legalisiert wurde hatte?</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.7558501958847046</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.7950262427330017</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7684102058410645</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.7787602543830872</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.7599204182624817</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>154</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hey, ich habe in den Nachrichten gehört, dass Deutschland die Ukraine im Krieg mit Waffen beliefert. Was sind die Vor und Nachteile? Sollte ich das also unterstützen oder ablehnen? Was umfasst ein Gesselschaftsdienst in Deutschland? Gibt es also Gesellschaftlich mehr Vorteile als Nachteile? Gibt es private Nachteile und wenn sie gering sind wieso wird der Dienst nicht eingfeführt? Was spricht für die Legalisierung der aktiven Sterbehilfe? Wieso gibt es dann trotzdem Leute die sie ablehnen?</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.681699812412262</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.7150803804397583</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.6922069191932678</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.6985316276550293</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.6996546387672424</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>155</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hi, ich würde mich gern mit folgendem Thema auseinandersetzen: Seit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert. Gerne würde ich meine Meinung dazu ausarbeiten. Kannst du das mit mir in einem Dialog erarbeiten, zB auch mit Rückfragen? Danke! In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden.
+Mit dieser Frage würde ich mich gern auseinandersetzen, bzw. wie ich dazu stehe. Kannst du das mit mir erarbeiten? Gerne auch mit Rückfragen. Danke! Hi, ich beschäftige mich aktuell mit dem Thema aktive Sterbehilfe und deren Legalisierung in Deutschland. Kannst du mir Informationen zusammenfassen, um mir eine Meinung zu bilden, und die mit Kontroverser Diskussion füttern? Danke!</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.733481228351593</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.7676903009414673</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7567481398582458</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.7583798766136169</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.7405232191085815</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>157</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Wie viele Waffen liefert Deutschland im Kampf gegen die Ukraine jährlich an die Ukraine und welche Einstellungen teilt die EU? Wie viel Geld würde der Regierung ein verpflichtendes soziales Jahr junger Menschen in Deutschland kosten? Würde dadurch mehr Geld eingespart  oder ausgegeben werden? Wirtschaftslage in Deutschland bei einem verpflichtenden sozialen Jahr junger Menschen zwischen 18 und 28 Jahre Unter welchen Bedingungen ist die aktive Sterbehilfe in Deutschland erlaubt und wurde sie in anderen Ländern bereits vollständig legalisiert?</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.748867928981781</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.7784881591796875</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.7611976861953735</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.7636125087738037</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.7454349398612976</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>162</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Was passiert, wenn Deutschland die Waffen nicht liefert? Was hilft der Ukraine am meisten? Was sind die Alternativen? Was sind die Vor- und Nachteile von einem verpflichteten Gesellschaftsdienst? Wie soll das ablaufen? Verdient man dabei Geld? In welchen Fällen ist aktive Sterbehilfe kritisch zu sehen? Was ist, wenn Menschen aufgrund ihrer Krankheit nicht in der Lage sind, eine solche Entscheidung zu treffen? In welchen Fällen ist es eine gute Sache?</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.687633216381073</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.7190067768096924</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.6923393607139587</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.7017503380775452</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.7030959129333496</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>164</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Schreib mir die eine zusammenfassung der geschichte der " deutschen waffenlieferung an die ukraine"
+Und füge bitte kritische literatur zu den folgen der waffenlieferungen hinzu Schreib mir eine kritische Zusammenfassung zum thema: verpflichtender gesellschaftsdienst in Deutschland Schreib mir eine kritische Zusammenfassung bezogen auf das Thema: aktive sterbehilfe in deutschland.</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.6668097376823425</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.6916574835777283</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.6928939819335938</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.6897020936012268</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.6702543497085571</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>165</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Inwiefern unterstützt Deutschland waffentechnisch die Ukraine gegen den russischen Angriffskrieg. Ist diese Unterstützung essentiell für die Verteidigung der Ukraine. Wie hoch ist die wirtschaftliche Belastung die Deutschland damit auf sich nimmt. Was würde passieren wenn diese Waffenlieferungen ausbleiben. Erkläre mir mögliche Szenarien für einen Gesellschaftsdienst in Deutschland. Berücksichtige dabei die Punkte die gerade in der Politik diskutiert werden. Wie ist die momentane rechtliche Grundlage zur Sterbehilfe. Enthält sie Einschänkungen oder Aussnahmen? Welche politischen Standpunkte gibt es momentan zum Thema Sterbehilfe. Liste die einzelnen Argumente zu jedem Standpunkt auf</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.7283157110214233</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.7698860764503479</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.747489869594574</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.7577019929885864</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.730381190776825</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>172</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Hallo, bitte liefere mir eine Liste mit pro und contra Punkten, ob und warum Deutschland Waffen an die Ukraine liefern sollten, mit Hintergrund des Angriffskrieges Russlands. Hi, bitte gieb mir eine Liste mit pro und contra Punkten, ob es in Deutschland für junge Menschen nach dem Schulabschluss ein verpflichtendes Jahr mit Gesellschaftsdienst geben sollte. Danke! Hallo, ich persönlich bin absolut für die Sterbehilfe aber kannst du mir bitte ein paar Punkte nennen, die dagegen sprechen? Bitte schließe religiöse Punkte aus.</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.6994757652282715</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.7342022061347961</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.7226686477661133</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.7284305095672607</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.7065581679344177</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>173</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Wie viel Geld wird seit dem Ukraine-Russland Krieg für Waffen etc. Ausgegeben? Welche spezifischen Aufgaben müssten Personen die im Gesellschaftsdienst arbeiten erfüllt werden? Für welches Alter soll der Gesellschaftsdienst gelten? In welchen Fällen kann eine Sterbehilfe Vorteilhaft sein? Warum ist Sterbehilfe in Deutschland illegal?</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.7428836226463318</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.7709684371948242</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.7426424026489258</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.753401517868042</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.7374950647354126</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>174</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ich befasse mich mit der moralischen Implikation von Waffenlieferungen im Kriegsfall, speziell geht es um den Krieg in der Ukraine. Deutschland liefert Waffen als militärische Unterstützung in die Ukraine. Ich möchte mir ein umfangreiches, reflektiertes Meinungsbild dazu bilden. Nenne mir ausführliche pro und contra Argumente und reflektiere diese anschließend. Mir ist es wichtig ein umfassendes Bild zu haben, gebe sowohl Meinungen wieder die vielleicht nur wenige Menschen haben als auch eine breite Öffentlichkeitseinschätzung. Nenne dafür unbedingt Quellenangaben. Ziel ist es mich am Ende für eine Position zu entscheiden oder zumindest über "alle" Seiten der Diskussion im Diskurs informiert zu sein. "In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden." Setze dich damit kritisch auseinander und gebe mir Pro und Contra argumente. Ich möchte mich dahingehend weiter informieren und mir eine Meinung bilden, hilf mir dabei. "In Deutschland ist die aktive Sterbehilfe (Tötung auf Verlangen) verboten. Es wird jedoch immer wieder diskutiert, ob sie unter bestimmten Bedingungen legalisiert werden sollte — etwa bei unheilbaren Krankheiten und auf ausdrücklichen Wunsch der betroffenen Person." Setze dich damit kritisch auseinander und gebe mir ein umfassendes Meinungsbild dazu.</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.7358075976371765</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.7716451287269592</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.7522555589675903</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.7599942088127136</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.7455883026123047</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>176</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Hallo, Deutschland liefert ja momentan Waffen an die Ukraine, im Zuge des Angriffskriegs durchs Russland. Kannst du mir verschiedene Argumente nennen, warum, oder warum nicht, Deutschland Waffen an die Ukraine liefern sollte. Am besten Stichpunktartig und übersichtlich. Kannst du mir zu diesen Argumenten auch die Quellen nennen, bzw Reverenzpunkte. Hallo welche Vor- und Nachteile hätte ein ein verpflichtender Gesellschaftsdienst für junge Menschen ? Wie sehen diese Vor-/Nachteile aus, wenn sich der Gesellschaftsdienst allein auf soziale, ökologische oder militärische Aufgaben bezieht? Gerne als übersichtliche Liste oder Tabelle Hallo, kannst du mir verschiedene Argumente nennen, mit deren Hilfe ich mich besser zu Frage "Soll Sterbehilfe in Deutschland verboten bleiben", positionieren kann ? Könntest du mir dazu auch entsprechende Quellen nennen? Gerne auch in Kombination mit Rechtssprechungsentscheidungen, vor allem bzgl. der Insulin-Entscheidung des BGH.</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.7272027730941772</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.7673826813697815</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.7471641302108765</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.7514140009880066</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.7464126944541931</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>179</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Warum sollte Deutschland keine Waffen an die Ukraine liefern? Erkläre mir bitte mehr zum Thema verpflichtender Gesellschaftsdienst für junge Menschen in Deutschland. Warum wird in Deutschland die aktive Sterbehilfe immer noch nicht legalisiert?</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.6998500227928162</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.7257835865020752</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.7112674117088318</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.7153742909431458</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.692199170589447</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>181</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deutsche Waffen an die Ukrainie liefern? verpflicheteder Gesellschaftsdient für junge Menschen in Deutschland, ist das sinnvoll? Wie ist die aktuelle Lage in Deutschalnd zur akruven Sterbehilfe? Was spricht für und gegen die aktive Sterbehilfe?</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.6071968078613281</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.630918025970459</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.6169544458389282</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.6224479675292969</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.6109506487846375</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>182</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Ist es vertretbar, dass Deutschland Waffen und militärische Ausrüstunf an die Ukarinie liefert? verpflichtende Gesellschaftsdienste in Deutschland? Vor- und Nachteile? Aktive Sterbehilfe erlauben? Wie ist es in anderen Ländern?</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.6299691200256348</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.6605021357536316</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.6372296214103699</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.6452630758285522</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.6214596629142761</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>184</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Seit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert. (erkläre warum Deutschland Waffen an die Ukraine liefert und, ob es sinnvoller wäre damit aufzuhören "Hintergrund:
+In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden." schreibe hierzu eine Abwägung von pro und Contra und nenne dabei die gefundenen Quellen Hintergrund:
+In Deutschland ist die aktive Sterbehilfe (Tötung auf Verlangen) verboten. Es wird jedoch immer wieder diskutiert, ob sie unter bestimmten Bedingungen legalisiert werden sollte — etwa bei unheilbaren Krankheiten und auf ausdrücklichen Wunsch der betroffenen Person.
+Was sind Pro und Contra Argumente der aktiven Sterbehilfe?</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.7731503248214722</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.801616370677948</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.7777820229530334</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.7904059886932373</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.767619252204895</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>185</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Wie siehst du die Waffenlieferungen von Deutschland an die Ukraine? Wie ist die aktuelle Diskussion über einen verpflichtenden Gesellschaftsdienst in Deutschland Wie ist die aktive Sterbehilfe in Deutschland geregelt Wie ist die rechtliche Situation von aktiver Sterbehilfe in Deutschland</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.5781522989273071</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.6151002645492554</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.6046151518821716</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.6099866032600403</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.5868710279464722</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>186</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ist es gut dass deutschland waffen an die ukraine schickt? wie unterstützt deutschland die ukraine wohin exportiert deutschland sonst noch waffen früher gab es ja den wehrdienst, was hat so einer für vor und nachteile? gibt es da vergleiche zu anderen ländern? warum wurde der dienst eigentlich damals abgeschafft? wie ist die rechtliche lage um die sterbehilfe in deutschland? kannst du mir eine pro und kontra liste erstellen was denkst du darüber?</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.6698677539825439</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.6982550621032715</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.6910814046859741</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.6900230646133423</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.6720014810562134</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>187</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Gib mir bitte Zahlen, Daten und Fakten zur militärischen bzw. kriegsbedingten finanziellen Unterstützung der Ukraine durch Deutschland seit 2022 (bitte, wenn möglich, einzeln nach Jahren aufgelistet). Gib mir dazu weitere Daten, inwiefern die Ukraine durch andere Länder finanziell bzw. militärisch unterstützt wird/wurde. Bitte gib mir außerdem eine Liste, wo es in den letzten Jahren seit diesem Zeitraum (2022) Sozialkürzungen in Deutschland gab (auch wieder mit Jahreszahl und möglichst genauen Angaben, um wie viel was gekürzt wurde) Bitte gib mir die Daten zu Engangement-Zahlen (Bundesfreiwilligendienst) seit seiner Einführung, d.h. Wie viele Menschen leisten pro Jahr einen BFD? Wie waren die Zahlen in den Jahren, als es noch einen verpflichtenden Wehr- bzw. Zivildienst gab? Also: Wie viele Menschen leisteten damals den Dienst über die Jahre?
+Und: Wie sieht es mit dem Freiwilligen SOzialen Jahr aus (Zahlen)? 
+Gibt es Statistiken, wie sich das Absolvieren dieser Dienste über die Jahre verändert hat und was die Ursachen dafür sein könnten? (Bitte mit Quelle!) Bitte gib mir die gängigen Argumente, die für und gegen aktive Sterbehilfe in Deutschland sprechen. Gib mir gerne, falls verfügbar, wissenschaftliche Quellen zu den einzelnen Punkten. Meines Wissens gibt es bereits seit einigen Jahren bestimmte Vereine, die auch in Deutschland Assistenz zum Suizid nach einem strengen Prüfverfahren und verbunden mit beträchtlichen Kosten anbieten. Wurde das revidiert oder sind diese Vereine weiterhin tätig?</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.7520714402198792</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.7767777442932129</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.7695022821426392</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.7702057361602783</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.7512122988700867</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>190</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Was sind Argumente für oder gegen Waffenlieferung an die Ukraine Mit Quellenangaben FSJ/ Soziales Jahr verpflichtend machen in Deutschland Argumente dafür oder dagegen wird Wehrpflicht mit einbezogen bei diesen Ergebnissen Gebe mir pro contra Argumente für sterbehilfe, mit ausführung Welche Gruppen sind tendenziell für welche Meinungen in diesem Thema</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.7529295086860657</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.8022851347923279</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.784883975982666</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.7924109101295471</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.7464032769203186</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>199</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deutschland liefert ja seit dem russischen Angriffskrieg gegen die Ukraine Waffen und militärische Ausrüstungen an die Ukraine. Ich weiss nicht genau was ich davon halten soll, was sagst du dazu? Ich habe mitbekommen, dass in Deutschland das Thema "Gesellschaftsdienst für junge Menschen" diskutiert wird und ob dieses Gesetz eingeführt werden sollte. Gebe mir einige Informationen zu den genannten Diskussionen und nenne mir mindestens 5 Vor und Nachteile. Danke :) Du weisst doch von dem Verbot der aktiven Sterbehilfe in Deutschland, richtig? Es wird jetzt immer wieder darüber diksutiert ob dies vielleicht doch Legalisiert werden sollte, jedoch unter bestimmten Bedinungen (bsp. unheilbare Krankheit). Was sagst du dazu?</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.7357035279273987</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.7634257078170776</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.7442860007286072</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.7539247870445251</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.7459848523139954</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>209</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Was liefert Deutschland aktuell für Waffen an die Ukraine? Was sind aktuelle Pläne &amp; Daten zur Waffenlieferung in die Ukraine? Aktueller Stand Russland-Ukraine-Krieg Was sind Vor- und Nachteile eines verpflichtenden Gesellschaftsdienst? Was hat ein verpflichtender Gesellschaftsdienst für Folgen für junge Menschen? Was gibt es für Möglichkeiten um einen Gesellschaftsdienst zu absolvieren? Pro- und Kontra-Argumente aktive Sterbehilfe aktuelle Rechtslage Sterbehilfe, genau erklärt</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0.7198766469955444</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.7476515173912048</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.7330478429794312</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.7398937344551086</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.7050843238830566</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>217</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Welche und wie viele Waffen wurden seit Februar 2022 von Deutschland an die Ukraine geliefert? Gibt es Quellen, die den Einsatz dieser Waffen zeigen? Wie viele Stellen in sozialen oder militärischen Einrichtungen und in der Pflege sind momentan in Deutschland unbesetzt und könnten realistisch von jungen Menschen in einem verpflichtenden Dienstjahr übernommen werden? Gibt es Meinungen von jungen Menschen, die einen solchen (oder einen vergleichbaren) Dienst absolviert haben? Gibt es Meinungen von berufstätigen Menschen, die mit jungen Menschen in einem solchen (oder vergleichbaren) Dienst gearbeitet haben? Gibt es Meinungen von Menschen, die von jungen Menschen in einem solchen (oder vergleichbaren) Dienst gepflegt wurden? Wie läuft die aktive Sterbehilfe in Ländern wie der Schweiz konkret ab? Welche Richtlininen existieren dort und welche Anforderungen sind dort erforderlich, um die aktive Sterbehilfe in Anspruch zu nehmen?</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0.7296301126480103</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.7513594031333923</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.7394983768463135</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.7400668263435364</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.7327191233634949</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>218</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Gib mir pro und contra listen dafür, ob Deutschland waffen an die Ukraine liefern sollte. welche meinungen gibt es zu einem verpflichtenden dienst nach dem Schulabschluss und was denkst du dazu was wären vorteile einer legalisierung der sterbehilfe in Deutschland ? sollte man aus ethischen gründen die sterbehilfe legalisieren?</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0.7278158664703369</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.7726364731788635</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.7521445751190186</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.7636879682540894</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.7256293892860413</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>228</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Wie ist die Beziehung zwischen Deutschland und Ukraine seit dem Krieg hinsichtlich der Unterstützung Welche Auswirkungen könnte der diskutierte verpflichtende Gesellschaftsdienst für junge Menschen haben? Kann man sich von bestimmten Aufgaben berefeien oder mit etwas anderem ausgleichen? Erläutere mir die aktive Sterebehilfe in Deutschland</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0.7184493541717529</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.7406653165817261</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.7364399433135986</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.7315872311592102</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.7283165454864502</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>230</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Erstelle eine ausgewogene Übersicht der wichtigsten Pro- und Kontra-Argumente zur Frage, ob Deutschland Waffen an die Ukraine liefern sollte (im Kontext des Kriegs seit 2022).
+Struktur:
+Sicherheitspolitische Argumente (Pro/Kontra)
+Völkerrechtliche/moralische Argumente (Pro/Kontra)
+Eskalationsrisiko und Beziehung zu Russland (Pro/Kontra)
+Historische/deutsche Verantwortung (Pro/Kontra)
+Bündnispolitische Argumente (NATO, EU, USA) (Pro/Kontra)
+Wirtschaftliche und militärische Kapazitätsfragen (Pro/Kontra)
+Für jeden Punkt: Nenne die stärksten Argumente beider Seiten in 2-3 Sätzen, möglichst konkret und mit Bezug auf reale Positionen (z.B. von Parteien, Experten, internationalen Partnern). Vermeide eigene Wertungen, stelle stattdessen dar, wer welche Position vertritt und warum. Am Ende: kurze Übersicht offener empirischer Streitfragen (z.B. Wirkung auf Kriegsverlauf, Eskalationsgefahr). Erarbeite eine ausgewogene, evidenzbasierte Übersicht der Argumente für und gegen 
+die Einführung eines verpflichtenden Gesellschaftsdienstes in Deutschland 
+(z.B. als soziales Pflichtjahr für junge Erwachsene).
+Struktur:
+1. Kurze neutrale Einordnung: Was wird aktuell diskutiert (Dauer, Zielgruppe, 
+   Bereiche wie Pflege, Rettungsdienst, Bundeswehr, Umweltschutz)?
+2. Empirische Befundlage zu bestehenden Modellen:
+   - Welche Länder haben verpflichtende oder freiwillige Dienstmodelle 
+     (Schweiz, Österreich, skandinavische Länder, Israel, Südkorea etc.)?
+   - Welche Evaluationsstudien/wissenschaftlichen Untersuchungen existieren 
+     zu deren Wirkungen (z.B. auf Arbeitsmarktintegration, Ehrenamt-Quoten 
+     im Nachgang, gesellschaftlichen Zusammenhalt, psychische Gesundheit)?
+   - Gibt es deutsche Studien/Gutachten zum Bundesfreiwilligendienst oder 
+     historischen Wehr-/Zivildienst, die übertragbare Erkenntnisse liefern?
+3. Argumente DAFÜR – jeweils mit Verweis auf Studienlage, sofern vorhanden:
+   - Gesellschaftlicher/sozialer Nutzen (z.B. Untersuchungen zu Pflegekräftemangel)
+   - Individueller Nutzen (Studien zu Persönlichkeitsentwicklung, Berufsorientierung 
+     nach Freiwilligendiensten)
+   - Sozialer Zusammenhalt (sozialwissenschaftliche Studien zu Durchmischung)
+   - Kennzeichne explizit, wo es sich um empirisch gestützte Aussagen vs. 
+     plausible, aber unbelegte Annahmen handelt
+4. Argumente DAGEGEN – ebenfalls mit Studien-/Gutachten-Bezug:
+   - Verfassungsrechtliche Bewertungen (Gutachten des Wissenschaftlichen 
+     Dienstes des Bundestages, Rechtsgutachten zu Art. 12 GG)
+   - Ökonomische Studien (Kosten-Nutzen-Analysen, Berechnungen zu 
+     Opportunitätskosten für Ausbildung/Studium, z.B. vom ifo-Institut, 
+     IW Köln, DIW)
+   - Kapazitätsstudien (Sind genug Plätze/Anleitungspersonal vorhanden? 
+     Erfahrungswerte aus dem BFD-Ausbau)
+   - Gerechtigkeitsforschung (Studien zu Wehrgerechtigkeit, Gender-Aspekten)
+5. Methodische Einordnung:
+   - Wie belastbar ist die zitierte Studienlage (Stichprobengröße, 
+     Kausalität vs. Korrelation, Aktualität, Auftraggeber/Interessenkonflikte)?
+   - Wo bestehen Forschungslücken, zu denen es (noch) keine belastbaren 
+     Daten gibt?
+6. Fazit: Zentrale ungeklärte Streitpunkte, insbesondere dort, wo sich 
+   Studienlage und politische Debatte unterscheiden – ohne eigene Wertung.
+Wichtig: 
+- Unterscheide klar zwischen "Studie zeigt X" und "Institution/Politiker 
+  argumentiert X"
+- Nenne bei Studien nach Möglichkeit Urheber, Jahr und Methodik
+- Keine eigene Positionierung Sammle möglichst objektiv und ausgewogen die zentralen Argumente zum Thema Sterbehilfe. Gehe dabei wie folgt vor:
+Begriffsklärung: Unterscheide zwischen den relevanten Formen (aktive, passive, indirekte Sterbehilfe, Beihilfe zum Suizid) und erkläre kurz die rechtliche Einordnung in Deutschland/Europa.
+Argumente dafür, gegliedert nach Perspektiven:
+Selbstbestimmungsrecht / individuelle Autonomie
+Medizinisch-ethische Sicht (Leidminderung)
+Rechtliche/gesellschaftliche Entwicklungen (z. B. Verfassungsgerichtsurteile)
+Argumente dagegen, gegliedert nach Perspektiven:
+Lebensschutz / Menschenwürde
+Missbrauchs- und Druckrisiken (z. B. gegenüber vulnerablen Gruppen)
+Religiöse/weltanschauliche Positionen
+Alternativen wie Palliativmedizin und Hospizarbeit
+Kontroverse Grenzfragen: Nenne Punkte, bei denen selbst Befürworter und Gegner innerhalb ihrer jeweiligen Lager uneinig sind (z. B. Sterbehilfe bei psychischen Erkrankungen, Minderjährigen).
+Quellenhinweis: Gib an, worauf sich die Argumente stützen (ethische Theorien, Studien, Gerichtsurteile), ohne selbst eine Wertung oder Empfehlung abzugeben.
+Vermeide eine abschließende persönliche Bewertung – das Ziel ist eine möglichst neutrale Gegenüberstellung.</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0.8179793953895569</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.8721047639846802</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.8432492613792419</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.8559889197349548</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.8202051520347595</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>237</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Welche Auswirkungen hätten weitere Waffenlieferungen auf die Ukraine, Deutschland, Europa und den Verlauf des Krieges? Bitte nenne sowohl mögliche Chancen als auch Risiken. Welche Länder haben schon einen verpflichtenden Gesellschafts oder Militärdienst und wie sind dort die Erfahrungen und was könnte für Deutschland relevant sein? Welche ethischen und rechtlichen Argumente sprechen für bzw. gegen eine Legalisierung von der aktive Sterbehilfe? Bitte erläutere auch mögliche Risiken und Schutzmaßnahmen.</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0.746633768081665</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.7819616198539734</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.7552915811538696</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.76875239610672</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.7421693801879883</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>244</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sollte Deutschland weiterhin Waffen an die Ukraine liefern? Was sind gründe dafür und dagegen? Sollte ein GEsellschaftsdienst für junge Menschen eingeführt werde? Was sind die Argumente die dafür und dagegen sprechen Was sind Gründe für und gegen die aktive Sterbehilfe? Sollte es in Deutschland legalisiert werden?</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0.7070935964584351</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.7414779663085938</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.7149223685264587</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.7281633019447327</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.7081993818283081</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>247</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Du weißt ja sicher, dass Deutschland im Zuge des Ukraine-Krieges schon länger und weiterhin Waffen im großen Umfang an die Ukraine liefert. Ich bin generell gegenüber Kriegshandlungen jeder Art negativ eingestellt, verstehe aber natürlich die Notwendigkeit einer Aufrechterhaltung von Verteidigung. Bitte versuche so neutral wie möglich deine eigene Stellung zu dem Thema zu beziehen, und liefere mir für jede deiner Aussagen stichhaltige Begründungen und Quellen, wenn zitiert. Bitte liefere mir mehr Infos zum früheren Wehr- bzw. Sozialdienst und wie dieser heutzutage ausgestaltet ist. Was ist deine Meinung zu einer möglichen generellen Wiedereinführung? Was für Vorteile und Nachteile hat so ein System? Und gibt es ähnliche Systeme in anderen Ländern? Wie (gut) funktionieren sie da? Wie ist deine Position zur Legalisierung von Sterbehilfe in Deutschland? Ich persönlich fände wahrscheinlich eine Entkriminalisierung bei nachweisbarem Einverständnis des Patienten statt einer pauschalen Legalisierung das beste, bin aber definitiv kein Rechtsexperte. Bitte bezieh selbst sachlich Stellung zu dem Thema und ordne auch meine Idee einmal sinnvoll ein.</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0.7246884703636169</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.7675019502639771</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.741351306438446</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.7528015375137329</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.7366191744804382</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>256</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Stelle das Pro und Kontra von Deutschlands Waffenlieferungen an die Ukraine seit Februar 2022 gegenüber. Fasse die Argumente zusammen, wegen derer das Thema Waffenlieferungen von Deutschland an die Ukraine kontrovers diskutiert wird. Welche Positionen gibt es zu einem verpflichtenden Gesellschaftsdienst für junge Menschen (sozial, ökologisch, militärisch), z.B. nach dem Schulabschluss? Nenne die Argumente der jeweiligen Positionen. Welche Vor- und Nachteile hätte ein verpflichtender Gesellschaftsdienst für die verschiedenen Akteure und Interessensgruppen? Welche Meinungen gibt es zur aktiven Sterbehilfe (Tötung auf Verlangen)? Stelle verschiedene Positionen mit Argumenten einander gegenüber. Stelle kurz dar wie verschiedene Länder Sterbehilfe rechtlich geregelt haben und welche Vor- und Nachteile die jeweiligen Regelungen haben.</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0.7654604911804199</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.8084679841995239</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.7859817147254944</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.7956865429878235</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.7652549147605896</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>259</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Hintergrund:
+Seit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert.
+Aufgabe:
+Ich möchte einen KI-Chatbot nutzen, um mich mit der Frage auseinanderzusetzen, wie ich dazu stehe, dass Deutschland Waffen an die Ukraine liefert. Stelle Fragen, bevor du ausführst. Hintergrund:
+Seit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert.
+Aufgabe:
+Ich möchte einen KI-Chatbot nutzen, um mich mit der Frage auseinanderzusetzen, wie ich dazu stehe, dass Deutschland Waffen an die Ukraine liefert. ERstelle einen Prompt, der mir dabei hilft, eine Meinung zu bilden. Stelle Fragen, bevor du ausführst. In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden. Gib mir weitere Hintergrundinformationen, damit ich mir selber ein Bild machen kann und die Frage beantworten kann, wie ich selber zu dem Thema stehe. Stelle Fragen, bevor du ausführst. Gib mir Hintergrundinformationen zur Legalisierung von aktiver Sterbehilfe in Deutschland. Führe Pros und Kontras auf. Stelle Fragen, bevor du ausführst.</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0.726592481136322</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.7546559572219849</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.7424580454826355</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.7473502159118652</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.7290070056915283</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>265</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>HAllo, Deutschland liefert ja seit dem Anfriffskrieg von Russland Waffen an die Ukraine. Ich würde gerne rausfinden, wie ich selbst dazu stehe, kannst du mir mit mir heir MEinungs PingPong spielen und mich danach bewerten? Die Boomer BAstarde wollen mal wieder die jungen MEnschen mit einem "verpflichtenden GEsellschaftsdienst" knechten ... wie cih wirklich dazu stehe würd eich gerne mit diesem Chat hier rausfinden Aktive Sterbehilfe ist in Deutschland verboten - selbst bin ich sehr unsicher, wie ich dazu stehe ... könnten wir darüber sikutieren, damit ich mich da einordnen kann?</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.6990922093391418</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.7293033003807068</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.7155059576034546</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.718693733215332</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.7283787727355957</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>275</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ich will fundiert Hinterfragen Deutschland Waffen und militärische Ausrüstung an die Ukraine liefern sollte. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert. Ich habe hier eine feste Meinung auf "ja" und Begründe dies mit der absoluten Notwendigkeit militärischer Abschreckung als einziges wirksames Mittel, auch wenn damit hohe gesellschaftliche (Opportunitäts)Kosten verbunden sind, die ich aber als geringfügiger als eine echte militärische Auseinandersetzung erachte. Falls es zu letzterer käme bräuchten wir aber ohnehin auch militärische Ausrüstung entsprechende Vorlaufzeit zur Herstellung. Diskutiere und challenge mich nachdrücklich mit Gegenargumenten der Seite für "keine Waffenlieferungen". Ich bin ein normaler Bürger. Ich möchte mich kritisch mit dem Thema "verpflichtender Gesellschaftsdienst für junge Menschen" auseinandersetzen, z. B. um eine Position in einer Dikussion vertreten zu können und um informierte Wahlentscheidungen zu treffen. Einordnung des Themas: In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden.
+Bereite mit Pro- und Contra-Argumente auf. Nutze dafür Studien, Nachrichtenartikel, PDFs oder sonstige Angaben im Internet, wenn möglich mit Quellenangabe. Ich will mich zum Thema "Legalisierung aktiver Sterbehilfe in Deutschland" informieren. HIntergrund: In Deutschland ist die aktive Sterbehilfe (Tötung auf Verlangen) aktuell noch verboten. Es wird jedoch immer wieder diskutiert, ob sie unter bestimmten Bedingungen legalisiert werden sollte — etwa bei unheilbaren Krankheiten und auf ausdrücklichen Wunsch der betroffenen Person.
+Bereite mir eine Liste mit Pro und Kontra Punkten auf, jeweils mit belastbaren Quellen. Nutzen dafür Nachrichten, Studien und auch Beispiele aus anderen Ländern, sowie Daten/Informationen zur Inanspruchnahme aktiver Sterbehilfe und möglicher kriminellen Aktivitäten in diesem Zusammenhang.</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0.7767050862312317</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.811762809753418</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.7891237139701843</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.7996686100959778</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.7728288173675537</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>293</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Welche Diskussionspunkte werden vorgeführt (pro/contra)? Welche Gruppierungen stehen hinter den jeweiligen Standpunkten? Wie würde diese Regelung die Ausbildungsberufe beeinflussen, da es in vielen momentan zu wenig Azubis haben? Was gibt es für Argumente (pro und contra)? Von wem wird diese Regelung angeleitet (Politische Partei, andere Interessengruppen,...)? Welche Bedingungen sollen denn aufgestellt werden? wie würde man seinen ausdrücklichen Wunsch formulieren müssen und wie würde es mit kognitiven Krankheiten wie Demenz oder Alzheimer funktionieren? Wie wird in diesem Zusammenhang die passive Sterbehilfe in der Diskussion behandelt?</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.7432490587234497</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.7874064445495605</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.7640397548675537</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.7724543809890747</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.7562832236289978</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>294</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Hi, welche Waffen werden momentan von Deutschland/EU/Nato an die Ukraine geliefert und in welchem Umfang? Gibt es Waffenarten, die nicht geliefert werden? Wie steht das im Verhältnis zu Lieferungen in andere Kriegsgebiete? Gibt es im Grundgesetz eine Grundlage für Waffenlieferungen? In einem Land in dem Frienden und Menschenleben geschätzt werden, aber ebenso die Freiheit scheint es politisch nicht ganz eindeutig zu sein, ob man Sicherheit der 'westlichen' Welt über Menschenleben in Kriegsgebieten stellen sollte. Gibt es für sowas klare Regelungen oder ist das eher eine persönliche Abwägung der Politiker? Wie viel hat die deutsche Wirtschaft von dem höheren Maß an Waffenproduktion gewonnen? Gibt es Hinweise darauf, dass Politiker in die Waffenlobby / Waffengeschäfte verstrickt sind, und davon aktiv profitieren würden? Wenn ja, welche und in welchem Umfang? Hi, kannst du mir ein bisschen Hintergrundinfo zu dem Gesellschaftsdienst geben? Wie lange soll der dauern? In welchem Alter? Welche Ausnahmen werden diskutiert? Wie unterscheidet er sich von dem alten Wehr- oder Sozialdienstsystem? Können die jungen Menschen frei wählen, wo sie den Dienst leisten wollen? Wie sieht die finanzielle Unterstützung während des Dienstes aus? Kann der Dienst auch im Ausland absolviert werden? Wie sehen aktuelle Entwürfe aus, den Dienst einzuführen? Gibt es bereits die nötige Infrastruktur? Genug Plätze und Projekte wo junge Menschen ohne Hintergrundwissen gebraucht würden? Genug Budget um die jungen Menschen während der Zeit zu bezahlen/unterstützen? Hi, kannst du mir ne grobe Übersicht über die gängigsten Pro und Kontraargumente bzgl Sterbehilfe machen? In welcher Form wird eine Umsetzung in Deutschland diskutiert? Was wären die Regeln, wie würde das Gesetzt wahrscheinlich (lt aktuellen politischen Diskussionen) denn implementiert? Ich glaub in anderen Ländern gibt's das schon, oder? Belgien? Niederlande oder so? Wie läuft es dann da bisher? Wie wird das Angebot angenommen, und von wem? Gibt es schon Vor und Nachteile, die sich abzeichnen, oder ist es dafür noch zu früh?</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0.7135363817214966</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.7450141906738281</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.7288948893547058</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.7320401072502136</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.7256494760513306</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>301</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Hey, kannst du mir erklären, um was es sich in dem Ukraine Kireig handelt? Und was hat Deutschland mit der ganzen Sache zu tun? Ich möchte mir eine Meinung dazu bilde, bitte gebe mir faktisch neutrale Infos. Hey, kannst du mir erklären, was es mit dem Gesellschaftlichen Dienst auf sich hat, der aktuell diskutiert wird? Hey, kannst du mir Infos zur Sterbehilfe geben und mir die aktuelle Lage in Deutschland erklären?</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0.6489037871360779</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.6862372159957886</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.6788569092750549</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.6785255074501038</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.6705693006515503</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>302</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Erkläre mir bitte genau die Waffenliefungen an die Ukraine von DE. Erläutere die Gründe und vorallem die großen Diskussionspunte? Wie würde ein verplichtender Gesellschaftsdienst in DE ablaufen? Welche Vorteile hat das? Erkläre mir die positiven und negativen Seiten an der Aktiven Sterbehilfe. Erkläre mir die Diskussionspukte um das Thema genau. Danke</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0.6395354270935059</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.6736191511154175</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.6612070798873901</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.663415253162384</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.6625171899795532</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>306</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Wie tragen waffenlieferungen von Deutschland in die Ukraine zum krieg bei. Was kann dabei in Deutschland passieren/was sind die folgen. Sage mir was der aktuelle stand zu verpflichtenden gesellschaftsdiensten in Deutschland ist. Nenne auch vor und Nachteile. Welche Länder auf der welt haben bereits aktive sterbehilfe legalisiert und wie läuft das Konzept vor Ort.</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0.653867781162262</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.6839809417724609</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.6750636696815491</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.6748800873756409</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.6558374166488647</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>307</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Warum sollte Deutschland weiterhin Waffen an die Ukraine liefern und warum nicht? Welche Vor- und Nachteile würde es mit sich bringen, wenn ein einjähriger verpflichtender Gesellschaftsdienst in Deutschalnd eingeführt wird? Nenne Vor- und Nachteile der aktiven Sterbehilfe</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0.7071878910064697</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.7420207858085632</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.7108286023139954</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.7217157483100891</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.7079573273658752</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>310</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Wie viel geldgibt Deutschland für die waffenindustrie aus? Wie viel Waffen bekommt und benötigt die Ukraine momentan Gesellschaftsdienste nach abi aktive sterbehilfe Methoden passive Sterbehilfe</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0.7191258668899536</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.7448944449424744</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.7347190380096436</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.7326894998550415</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.7178546190261841</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>311</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Sollte Deutschland weiterhin Waffen an die Ukraine liefern? Was sind die argumente für und was sind die argumente gegen die Waffenlieferung? Beachte bitte möglichst viele und vielfältige Perspektiven Was wären die Vor- und Nachteile eines Gesellschaftsdienst für junge Menschen, der soziale, ökologische oder militärische Aufgaben umfassen würde und z.B. nach dem Schulabschluss geleistet werden. Beachte bitte verschiedene Perspektiven Welche Punkte sprechen für und welche gegen aktive Sterbehilfe (Tötung auf Verlangen).  unter welchen Bedingungen wäre eine legalisierung denkbar?</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0.7578732371330261</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.7893972396850586</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.7662883400917053</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.776250958442688</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.7600353956222534</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>312</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Welche Gründe gibt es für Deutschland Waffen zu liefern? Erkläre Nenne Vorteile von Gesellschaftsdienst Warum wird dies momentan so schlecht bewertet? Warum darf man keine aktive Sterbehilfe durchführen? Nenne was sich ändern würde</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0.7638478875160217</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.8104910850524902</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.7722960710525513</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.7876083850860596</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.773980438709259</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>316</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Welche Informationen hast du über deutsche Waffenlieferungen an die Ukraine bzw. solche, die von Deutschland finanziert wurden? Mich interessieren Art(Kategorie und konkrete Typbezeichnug) und Quantität der Rüstungsgüter und der jeweilige Lieferzeitpunkt. Was ist über die Wirksamkeit der dieser Lieferungen bei den Verteidigungbemühungen der Ukraine gegen die russiche Invasion bekannt? Z.B Feedback von ukrainischen Soldaten, die mit der von Deutschland gelieferten Ausrüstung kämpfen, außerdem Verlustraten der gelieferten Güter, und Übersicht über die von diesen Lieferungen verurachten russischen Verluste. Außerdem interessiert mich die Wahrnehmung deutscher Unterstützung in der ukrainischen Öffentlichkeit. 
+Gebe mir auch noch Informationen über von Deutschland geleistete, nicht strikt militärische Unterstützung für die Ukraine. Stelle mir Informationen über den geplanten verpflichtenden Gesellschaftsdienst für junge Erwachsene in Deutschland zusammen. Ich will vor allem wissen, welche verschiedenen Bereiche, aber auch konkrete Verwendungen dafür in Frage und wo die entsprechenden Dienststandorte sind. Außerdem interessieren mich jeweils der Verdienst/Vergütung/Taschengeld und wie sich die jeweiligen Verwendungen/Tätigkeiten später im Berufsleben verwenden lassen bzw. welche Vorteile ich selbst dadurch gewinnen kann(z.B. Erlernen interessanter Zusammenhänge, Einblick in Berufe, Kontake knüpfen, fachliche Qualifikationen, usw.). Stelle mir eine Übersicht über die relevanten Stellen in deutschen Gesetzestexten zusammen, die die aktive Sterbehilfe betreffen. Fasse mir jeweils zusammen, wie die Rechtslage dazu in anderen Regionen gestaltet ist, dabei interessieren mich vor allem die Schweiz, Skandinavien, Kanada und die USA, gebe mir aber auch gern Informationen zu anderen Ländern, falls dort ausergewöhnliche Regelungen gelten. Gebe mir jetzt noch Infos über die Fallzahlen aktiver Sterbehilfe und daraus resultierender Verurteilungen in Deutschland und die Fallzahlen in den obigen anderen Regionen und auch die Ausweichmigration dorthin, um etwaige lockerere Regelungen zu nutzen.</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0.7359709739685059</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.7670904397964478</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.7531624436378479</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.7548231482505798</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.7415745258331299</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>317</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Auswirkungen der waffenlieferung an ukraine auf globalen süden und auf deutsche Bevölkerung Warum bemüht sich deutschland oder nato nicht um beendigung des krieges zwischen Ukraine und Russland? Welche vorteile hat wer von einem Kontinuieren des Krieges? Woher hat deutschland geld für waffenlieferung, während gesundheitssystem immer teurer wird und mieten explodieren bzw. Inflation seit ulraine krieg Unterschied verpflichtender gesellschaftsdienst und fsj/bfd Warum soll verpflichtender gesellschaftsdienst militärische Aufgaben beinhalten? Nenne vor- und nachteile der legalisierung aktiver sterbehilfe Warum ist aktive sterbehilfe in Deutschland verboten?</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0.7760714292526245</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.7955915927886963</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.778535008430481</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.785566508769989</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.7535274028778076</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>324</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Frage: Auf welcher Basis hat Deutschland entschieden Waffen an die Ukraine zu liefern?
+- Welche Argumente stehen sich gegenüber. Erstelle eine umfassende Analyse der Positionen.
+- In diesem Kontext sind viele nicht neutrale Informationen, gezielte Desinformation und Propaganda aufzufinden. Wie kann ich diese erkennen und dies in der Analyse berücksichtigen?
+- Wie kannst du als LLM sicherstellen, dass die Informationen korrekt sind?
+Form: Erstelle eine strukturierte Übersicht und fasse die ergebnisse am Ende zusammen. Hauptfrage: Was versteht man unter "Gesellschaftsdienst" in Deutschland? 
+Form: Erstelle eine strukturierte Übersicht und fasse die wichtigsten Erkenntnisse in einem Management Summary zusammen. Detailfragen: 
+- Welche Dienste fallen darunter?
+- Welche Zielgruppe betrifft dies? Und warum diese?
+- Wer sind Befürworter des Gesellschaftsdiensts und warum?
+- Wer sind Gegner des Gesellschaftsdiensts und warum?
+- Warum soll der Gesellschaftsdiensts verpflichtend sein? 
+Form: Erstelle eine strukturierte Übersicht. Detailfragen: 
+- Wie ist die Historie verpflichtender Gesellschaftsdienste in Deutschland?
+- Was sind Erkenntnisse über die Historie? Auch aus der Wissenschaft?
+- Wie handhaben andere europäische Länder diese Dienste?
+- Welches Problem soll damit gelöst werden?
+Form: Erstelle eine strukturierte Übersicht. Hauptfrage: Was bedeutet "aktive Sterbehilfe" in Deutschland?
+Form: Erstelle eine strukturierte Übersicht, die verschiedene argumentative Positionen gegenüberstellt und in den aktuellen gesetztlichen Rahmen einordnet. Fasse die Ergebnisse am Ende zusammen. - Wie ist der aktuelle Status?
+- Warum ist aktive Sterbehilfe nicht legal in Deutschland?
+- Wie steht die Wissenschaf dazu?
+- Wie stehen Betroffene und deren Familien zu diesem Thema? - Wie handeln andere Nationen in dieser Frage?</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0.7227877378463745</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.7675103545188904</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.7448562979698181</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.75169837474823</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.7423127293586731</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>329</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Nenne mir bitte Gründe dafür und dagegen, dass Deutschland die Ukraine mit waffen und militärischer Ausrüstung im Krieg gegen Russland Unterstütz Mir ist X, Y, Z besonders wichtig. A und B kannst du eher vernachlässigen. Erstelle eine überarbeitete Bewertung zum Thema Gebe mir Beispiele für die Ausgestaltung  eines verpflichtender Gesellschaftsdienst für junge Menschen in Deutschland. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden.
+Gebe mir dann eine Pro und Kontra Liste dazu aus. X und Y finde ich nicht gut. Z würde ich nur zustimmen wenn XYZ berücksichtigt wird.
+Bereite mir eine überarbeitete Zusammenfassung als Stellungsnahme für meine Meinung aus. Nenne mir Argumente für und gegen die aktive Sterbehilfe.
+Berücksichtige dabei sowohl Aspekte der Betroffenen Person (erkrankt) und der Angehörigen die ggf. darunter leiden.
+Bewerte auch die allgemeine rechtliche Situation in Deutschland für ein solches Gesetz. Mir ist das Recht auf Selbstbestimmung sehr wichtig. Allerdings gilt das für Angehörige und Betroffene. Die grundsätzliche rechtliche Lage wäre mir in Zweifelsfall egal. 
+Bitte erstelle eine Zusammenfassung für meine Position zu dem Thema.</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0.7332591414451599</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.7718176245689392</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.7506356239318848</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.7602158784866333</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.7419978976249695</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>330</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>deutschland hat ja waffen in die Unkraine geliefert. ich bin ja eignetlicht gegen unterstützung von kriegen aber hilft das den Menschen vor Ort damit weniger zivilisten sterben? hey, was ist ein verpflichteter gesellschaftsdienst? es gibt mal wieder diskusionen über die aktive sterbehilfe in eutschland. kannst du mir vor und nachteile aufführen die damit einhergehen</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0.6686763763427734</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.6857525110244751</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.6735487580299377</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.6761872172355652</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.6706265211105347</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>332</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Seit 2022 ist die Ukraine in einem Verteidigungskrieg, Die EU als ganzes und DE im einzelnen leisten Hilfe in Form von Geld und Waffenlieferungen aus eigenen Beständen. Die Ukraine ist nicht teil der NATO daher ist die Frage ob sich die Unterstützung der Ukraine weiterhin lohnt. Es ist bereits zu mehreren Kritischen situationen an NATO Grenzgebieten mit Russland gekommen , "verirrte Raketen/Drohnen", "verwirrte Piloten". Die Hilfeleistungen zur Ukraine hat im hinbilck auf einen Potentellen direken Krieg der NATO und Ukraine auch auswirkung auf die Kriegsfähigkeit der Mitgliedsstaaten. Wie kann all das Balanciert werden, Verteidigungsmittel benötigen akut die Ukraine, mittelbar ist aber auch die Sicherheit con NATO Staten gefährdet. Die Wehrplicht ist schon einige Jahre augesetzt, heute wird über ein "verplichtenden Gesellschaftsdienst" diskutiert. Einige Menschen machen nach Abschluss der Schulischen Bildung ein "Gap Year", dieses könnte verplichend werden, verbunden mit spezifischen Tätigkeiten die im Dienst der Gesellschaft stehen. Welche Gründe sprechen für ein Gesellschaftsdienst, was müsste Beachtet werden. Was sind Gründe für die Ablehnung einer solchen Regelung und welche Ausnahmen sollten getroffen werden. Sterbehilfe ist ein kontroverses Thema, manche Menchen die villeicht Leiden, einen "Schönen" Tod in guter Umgebung  haben möchten, oder einfach der Ansicht sind lange genug gelebt zu haben (manche alte Menschen), wollen die entscheidung haben ihrem leben ein selbstbestimmtes Ende zu setzten.
+* Erstelle eine Gegenüberstellung zwischen den Argumenten von Befürwortern und Gegnern der Aktiven Sterbehilfe.
+* Gib außerdem Beispiele von Ländern in denen Sterbehilte erlaubt ist, welche sind die Hauptargumente mit der sie Aktive Sterbehilfe Legal machen.</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0.7537358403205872</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.7780646681785583</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.7612587213516235</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.7655332684516907</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.7570099234580994</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>338</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Kannst du mir mal die Argumentationsgrundlage der deutschen Bundesregierung erläutern im Bezug auf die Waffenlieferungen und anhaltende Unterstützung der Ukraine und im zweiten Schritt dann bitte auch die Argumentationsgrundlage der Kritiker. Ist es aus deiner Sicht ein logischer und gerechter Schritt einen verpflichtenden Gesellschaftsdienst (Wehrpflicht, FSJ usw.) für junge Menschen einzuführen und was währen die Pro und Cons davon Aktive Sterbehilfe ist ja immer wieder ein Thema in Dt., zähle mir mal Pro und Con zu der Legalisierung auf</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0.6904177665710449</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.7209983468055725</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.7141270041465759</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.7175290584564209</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.7013392448425293</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>339</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>gib mir je 10 Argumente fuer und gegen Waffenlieferungen an die Ukraine gib mir je 10 Argumente fuer oder gegen einen verpflichtenden Gesellschaftsdienst fuer junge Menschen/ gib mir je 10 Argumente fuer und gegen die Legalisierung aktiver STerbehilfe in Deutschland</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0.6628875136375427</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.6916990280151367</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.6864659190177917</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.6909443140029907</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.6488584876060486</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>340</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ich möchte mehr über den Krieg in der Ukraine erfahren. Dabei geht es mir speziell um die Beteiligung von Deutschland und Waffenlieferungen von Deutschland an die Ukraine. Ich suche Zeitungsartikel aus großen Zeitschriften (die Zeit, FAZ etc.) die dazu kritisch Stellung beziehen und Hintergründe erläutern. Im besten Fall möchte ich Artikel, die eher für und welche die eher gegen waffenlieferungen sind Ich möchte mich mehr mit dem Wehrdienst in Deutschland beschäftigen. 
+Kannst du mir erklären, wie das aktuell gehandhabt wird. Dazu würde mich auch interessieren, wie die Regelung früher war, bevor der Wehrdienst abgeschafft wurde. Damals gab es doch die Möglichkeit, stattdessen einen Zivildienst zu absolvieren, oder? Gibt es sowas heute auch wieder? Aktuell wird über einen gesellschaftsdienst diskutiert, der den Wehrdienst ersetzten soll wenn ich das richtig verstehenden habe. Kannst du mir näher erläutern, was dazu aktuell in Deutschland diskutiert wird? Ich suche Zeitungsartikel aus großen, seriösen Zeitschriften, welche sich mit dem gesellschaftsdienst befassen Kannst du mir die aktuelle Rechtslage in Deutschland bezüglich sterbehilfe erläutern? Wie sieht die aktuelle Debatte bezüglich einer Legalisierung beziehungsweise Erweiterung der aktuellen Regeln aus? Kannst du mir zu diesem Thema seriöse Artikel empfehlen?</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0.7078534364700317</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.7434703707695007</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.7277191281318665</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.7327491641044617</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.7256084680557251</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>343</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Du bist ein deutscher Politik-Experte rund um das Thema Russland-Ukraine-Krieg. Das Ziel ist es zu diskutieren, ob Deutschland weiterhin Waffen an die ukraine liefern sollte. Liefere mir eine Pro- und Contra-Liste aus der Sicht Deutschlands. Diskutiere aus der Sicht verschiedener PErspektiven, wie z.B. eines junge Menschen und eines Politikers, was Gründe für und gegen die Einführung eiens verpflichtenden Gesellschaftsdienst für junge Deutsche sind. Du bist ein Experte für aktive Sterbehilfe in Deutschland. Wie kann man aktive Sterbehilfe in Deutschand legalisieren und auf welche Konflikte stoßt man dabei?</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0.7180322408676147</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.746680736541748</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.7384533882141113</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.7380032539367676</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.7218454480171204</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>346</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Warum werden waffen geliefert? Was sind die ursachen für waffenlieferung? warum deutschland? Es wurde ja in der regierung diskutiert ob die wehrpflicht wieder aktiviert wird? was sind die argumente Ich habe eine Frage, wie steht Deutschland zur Sterbehilfe? Und was sind mögliche pro/contra argumente? was sind gute argumente gegen oder für sterbehilfe</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0.7004377245903015</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.7386056184768677</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.7069057822227478</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.7238834500312805</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.7021890878677368</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>349</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Welche Argumente für und gegen Waffenlieferungen an die Ukraine existieren, aus Perspektive von
+* Expert:innen zur Verteidigung, inklusive Mitglieder des Militärs
+* Friedensforscher:innen
+* Ukrainer:innen die direkt selbst betroffen sind und fliehen mussten
+* Anarchist:innen die in der Ukraine gegen das russische Militär kämpfen ohne selbst Teil der Ukrainischen Streitkräft zu sein
+* Pazifist:innen Welche Gesetztesgrundlage für einen Gesellschaftsdienst existiert in Deutschland? Welche Punkte an der gegenwärtigen Debatte darüber behandeln einen Gesellschaftsdienst der sich von einem Zivildienst/Wehrdienst wie es vor 20 Jahren noch üblich war und in der Praxis nahezu frei wählbar war (nicht rechtlich doch der Prozess des Verweigerns war bereits so etabliert dass es de Facto nahezu eine freie Wahl war) unterscheidet. Gibt es Studien welche zeigen ob das Leisten eines Gesellschaftsdienstes zu einem anderen Verhältnis zur Gesellschaft und zu einem anderen Verhältnis zum Staat führt?
+Gebe Quellen. Gibt es Studien in wie fern persönliche Entwicklungen durch Leisten eines Gesellschaftsdienstes beeinflusst werden?
+Gebe Quellen. Wie liegt die gesetzliche Regelung zur Sterbehilfe in Deutschland? Was sind die Grenzen an denen passiv und aktiv unterschieden wird? Welche Perspektiven sprechen für und gegen eine aktive Sterbehilfe? Vergleiche jene in der Deutschen Debatte mit einer Debatte in einem Land in welchem die aktive Sterbehilfe legal ist (Niederlande z.B.) und einem Land in welchem die Sterbehilfe auch passiv nicht erlaubt ist. Welche Phylosophen setzten sich mit der Frage der Sterbehilfe auseinander und waren in der Geschichte wichtig? Gebe eine kurze Liste von Essays (mit Quellen) welche die Debatte in der Geschichte geprägt und auch verändert haben.</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0.7335134744644165</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.7667732238769531</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.7469565868377686</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.7531343698501587</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.7438143491744995</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>356</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Waffenlieferung deutschland an ukraine argumente pro contra verpflichtender Gesellschaftsdienst argumente pro contra Argumente aktive Sterbehilfe pro contra</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0.6889262795448303</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.7400745153427124</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.7224330902099609</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.7402783036231995</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.6592420339584351</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>360</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Hi, ich würde gerne die Diskussion zum Thema Waffenlieferungen an die Ukraine besser verstehen. Ich selbst habe grob die Meinung, dass wir mehr Waffen liefern sollten, auch solche mit größerer Reichweite. Meiner Meinung nach sind wir längst in einem Konflikt mit Russland und sehe nicht, dass hierdurch die Gefahr maßgeblich erhöht wird, dass wir selbst in einen heißen Krieg gezogen werden. Ich habe in keinster Weise Verständnis für die Argumentation, dass Russland sich durch die Nato bedroht fühlt und wir eine friedliche Lösung finden müssen. Ich weiß aber, dass diese Meinung selbstverständlich stark geprägt ist durch Medienkonsum, soziale Prägung etc. Ich möchte gerne wirklich verstehen, welche harten Fakten es zu diesem Thema gibt und vor allem wo es ernsthaften Meinungsspielraum gibt, sodass ich mir insgesamt eine besser fundierte Meinung bilden kann. Hi, ich würde gerne die Diskussion zum Thema "verpflichtender Gesellschaftsdienst für junge Menschen" besser verstehen. Ich selbst habe grob die Meinung, dass ein Gesellschaftsdienst sinnvoll ist, solange es keine Bevorzugung des Wehrdienstes gibt. Ich halte es für sinnvoll, jungen Menschen einen Eindruck davon zu geben wie unsere Gesellschaft davon abhängt, dass wir einander helfen. Ich denke aber auch, dass der volkswirtschaftliche Nutzen nicht unerheblich ist und dass dies durchaus eine Rolle bei der Diskussion spielen darf. Ich weiß aber, dass diese Meinung selbstverständlich stark geprägt ist durch Medienkonsum, soziale Prägung etc. Ich möchte gerne wirklich verstehen, welche harten Fakten es zu diesem Thema gibt und vor allem wo es ernsthaften Meinungsspielraum gibt, sodass ich mir insgesamt eine besser fundierte Meinung bilden kann. Hi, ich würde gerne die Diskussion zum Thema "Legalisierung der aktiven Sterbehilfe" besser verstehen. Ich selbst habe grob die Meinung, dass sie unter bestimmten Bedingungen (unheilbare Krankheit, ausdrücklicher Wunsch bei erwiesenermaßen gesundem Verstand (z.B. keine Depression)) sinnvoll sein kann. Ich finde es tendenziell gut, Freiheiten zu gewähren, solange man sich im Klaren ist welche negativen Begleiterscheinungen es in Einzelfällen geben kann. Ich weiß aber, dass diese Meinung selbstverständlich stark geprägt ist durch Medienkonsum, soziale Prägung etc. Ich möchte gerne wirklich verstehen, welche harten Fakten es zu diesem Thema gibt und vor allem wo es ernsthaften Meinungsspielraum gibt, sodass ich mir insgesamt eine besser fundierte Meinung bilden kann.</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0.7410193681716919</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.7821683287620544</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.7557618618011475</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.7642692923545837</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.7686719298362732</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>366</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Hintergrund:
+Seit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert.
+Aufgabe:
+Sie möchten einen KI-Chatbot nutzen, um sich mit der Frage auseinanderzusetzen, wie Sie dazu stehen, dass Deutschland Waffen an die Ukraine liefert.
+Erledige die Aufgabe und gebe mir einen Überblick. Sei präzise. Verifiziere deine Infos. Wenn du dir unsicher bist schreib (unsicher) Hintergrund:
+In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden.
+Aufgabe:
+Sie möchten einen KI-Chatbot nutzen, um sich mit der Frage auseinanderzusetzen, wie Sie zu einem verpflichtenden Gesellschaftsdienst in Deutschland stehen.
+Erledige die Aufgabe. Gebe mir eine Overview. In Deutschland ist die aktive Sterbehilfe (Tötung auf Verlangen) verboten. Es wird jedoch immer wieder diskutiert, ob sie unter bestimmten Bedingungen legalisiert werden sollte — etwa bei unheilbaren Krankheiten und auf ausdrücklichen Wunsch der betroffenen Person.
+Aufgabe:
+Sie möchten einen KI-Chatbot nutzen, um sich mit der Frage auseinanderzusetzen, wie Sie zur Legalisierung aktiver Sterbehilfe in Deutschland stehen.
+Erledige die Aufgabe. Gebe mir strukturiert Fragen und im Anschluss gebe mir einen Überblick.</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7706812620162964</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8007648587226868</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7803334593772888</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.7896683216094971</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.7759657502174377</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>367</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deutschland liefert ja Waffen bzw Ausrüstunf an die Ukraine, kommen die auch wirklich an? was sind das genau für gegenstände und haben diese überhaupt wirkung, sind die qualitativ hochwerig? Von wem werden diese Waffen hergestellt? Wie wird für diese Waffen bezahlt und welche EU Länder helfen der Ukraine noch in diesem Krieg? Kann man mit diesen Lieferungen den Krieg stoppen oder hat man gegen die Waffenmacht Russlands überhaupt eine Chance? Welche Verbesserungen könnte ein verpflichtendes Jahr für Deutscland haben, gibt es evtl Vergütungsvorschläge und wie ist die Infrastruktur dafür schon aufgebaut? Gibt es Löher um dieser Verpflichtung zu entkommen? Welche Argumente sprechen für die Legalisierung von Sterbehilfe, welche beispiele aus anderen Ländern kann man anbringen.
+Welche Argumente könnten gegen Sterbehilfe sprechen und warum wird das in Deutschland so gehandhabt?</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7332122921943665</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.7614349126815796</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7382073402404785</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.7460826635360718</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7382047176361084</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>368</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Pro contra waffenleiferung deutschlands an die Ukraine; linke prespektive Pro contra verpflichtenden Gesellschaftsdienst Pro contra Aktive sterbehilfe WO es bereits legal ist; wie läfts da?
+Wissenschaftliche Studien? Modelle aktiver Sterbehilfe</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0.7100281119346619</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.7582933902740479</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.7509881258010864</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.7550076246261597</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.7034050822257996</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>369</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Unter welchen Bedingungen liefert Deutschland aktuell Waffen an die Ukraine? Welche Vor- und Nachteile hätte ein verpflichtender Gesellschaftsdienst in Deutschland Welche Vorschläge haben unterschiedliche Politiker/Parteien für die Ausgestaltung eines verplischtenden Gesellschaftsjahr und befürworten sie ein solches grundsätzlich? Wieso ist aktive Sterbehilfe aktuell selbst wenn tödlich verlaufende Krankheiten vorligen aktuell verboten? Beziehe insbesondere die Tatsache mit ein, dass passive Sterbehilfe unter bestimmten Umständen erlaubt ist, aber wegen sehr hohen Kosten nur für Menschen in priveligierten Verhältnissen zugänglich ist.</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0.7601720690727234</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.7976582646369934</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.7677139043807983</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.7792259454727173</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.7639746069908142</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>376</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Was sind Argumente für und gegen die Waffenlieferung von Deutschland an die Ukraine Anhand welcher Quellen lassen sich die Argumente stützen Was bedeutet verpflichtender Gesellschaftsdienst. Welche Vor und Nachteile bringt er? Gibt es Möglichkeiten den Gesellschaftsdienst zu umgehen Warum ist Sterbehilfe in Deutschland nicht legal? Was sind Gründe für oder gegen die aktive Sterbehilfe?</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0.6853338479995728</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.7267323732376099</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.6992883086204529</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.7113803625106812</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.6939461231231689</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>378</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Was sind Gründe für und gegen Waffenlieferungen an die Ukraine. Gebe mir aus einer neutralen Perspektive heraus unterschiedliche Pros und Cons für die Lieferungen. Gehe auf unterschieldiche Perspektiven zum Thema ein und versuche so viele Gruppen und Akteure die davon betroffen sind in die Informationsbereitstellung einzubinden. Multiperspektivität ist gefragt. Nenne mir verschiedene Punkte die für oder gegen den verpflichtenden gesellschaftsdienst für junge Menschen in Deutschland spricht. 
+Gehe auf unterschiedliche Perspektiven ein. 
+Gehe auch auf mögliche Alternativen ein und differenziere die Vor und Nachteile eine verpflichtenden Dienstes. 
+Ich möchte gesellschaftliche, politische, ökonomische und Betroffenenperspektiven erfahren. Liefere mir unterschiedliche Sichtweisen zum Thema Sterbehilfe in Deutschland Legalisieren oder nicht. 
+Gehe auf verschiedene Perspektiven ein befürworter und Kritiker. 
+Ich möchte wissen wie betroffene sich zu diesem Thema äußern.
+Du sollst ein differenziertes Bild auf das Thema geben.</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6930140852928162</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.7353684902191162</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.7219131588935852</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.723040759563446</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.7106761932373047</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>379</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Ich bin eigentlich eher Unterstützerin der Linken, bzw. linker Politik, aber in einem Punkt geht meine Meinung da irgendwie in eine andere Richtung. Da wird ja häufig kritisiert, dass Deutschland Waffen liefert und ich finde das z.B. in Bezug auf Israel absolut richtig. Diese Waffenlieferungen sollte man sofort stoppen, weil Israel inzwischen einfach eindeutig der Aggressor ist. Bei der Ukraine ist das ja anders. Die Ukraine ist hier im Prinzip das Opfer und man muss ja einfach sagen, dass auch Deutschland gewissermaßen bedroht ist und es im Sinne der EU ist, die Ukraine zu unterstützen. Ich glaube, manche meinen, dass man keine Waffen mehr liefern sollte, damit der Krieg ein Ende hat. Aber das Ende wäre dann ja die Niederlage der Ukraine und das wäre doch einfach nicht richtig, oder? Keine Waffen liefern heißt ja nicht ein ausgehandelter Frieden. Putin setzt doch darauf, dass der Ukraine irgendwann die Kraft ausgeht. Oder gibt es tatsächlich noch negative Aspekte, die ich nicht benannt habe? Irgendwo scheint es am Ende fast nur eine finanzielle Frage zu sein, oder? Also auch die Frage, ob wir uns das leisten können. Weißt du zufälligerweise, wie groß die Ausgaben da sind? Gerade mal ins Verhältnis gesetzt zu anderen Ausgaben oder Einsparungen, wie jetzt irgendwie das neue GKV-Spargesetz oder aber Steuerhinterziehung Zurzeit wird ja ein verpflichtender Gesellschaftsdienst für junge Menschen diskutiert und ich hab eigentlich das Gefühl, dass das schon ne gute Idee wäre. Das könnte ja helfen, in sozialen Berufen wieder ein paar mehr Arbeitskräfte zu haben und gleichzeitig das Militär stärken, auch wenn ich denke, dass ein soziales oder ökologisches Jahr deutlich sinnvoller und auch wichtiger wäre. Ich hab selbst ein FSJ gemacht, das beeinflusst sicherlich auch meine Meinung. Aber eigentlich finde ich schon, dass wenig dagegen spricht. Klar ist es eine gewisse Einschränkung, aber überwiegen nicht die Vorteile? Gibt es wirklich triftige Gründe, die dagegen sprechen? Also übersehe ich etwas? Oder geht es bei der Frage tatsächlich darum, dass der Nutzen für die Gesellschaft der Freiheit des Einzelnen gegenübersteht? Ich versuche gerade die Debatte zur aktiven Sterbehilfe zu verstehen. Wenn ich das richtig sehe geht es ja darum, dass jeder das Recht haben sollte, in Würde und selbstbestimmt zu sterben und gleichzeitig will man verhindern, dass es Menschen das Leben kostet, die noch leben wollten. Fasst es das richtig zusammen? Also einerseits sollte man sterben dürfen und dabei auch unterstützt werden, wenn man vielleicht nicht mehr selbst in der Lage ist, ein Mittel zu schlucken oder so. Gerade bei neurodegenerativen Erkrankungen, wo Personen möglicherweise einfach nicht mehr in der Lage sind, irgendwas einzunehmen. Oder dass man sagen kann, man möchte aktive Sterbehilfe in Anspruch nehmen, wenn man dement wird und gar nicht mehr sagen kann, was man eigentlich will. Grundsätzlich finde ich das schon gut, weil das für jeden das Recht sein sollte. Gleichzeittig ist das Problem, dass Personen, die sich eben nicht mehr  äußern oder wehren können, aktive Sterbehilfe "aufgezwungen" werden könnte. Also dass sie im Endeffekt umgebracht werden, obwohl sie es nicht wollen, aber sich nicht äußern oder wehren können. Und das wäre natürlich fatal. Dann könnte es ein Arzt so hinstellen, als wäre es eben gewollte aktive Sterbehilfe, obwohl es dann eigentlich eher Mord oder Totschlag wäre. Sind das so die grundlegenden Argumente oder übersehe ich noch etwas? Welche Konsequenzen hätte das Ganze noch?</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0.714461624622345</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.750993013381958</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.7263163328170776</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.7339804172515869</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.7419525384902954</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>380</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>In welche Ausmaß liefert Deutschland Waffen an die Ukraine? Wie viel Geld kostet dem Deutschen Staat die Untersützung mit Rüstungsgütern? Wie viele Menschen wären von einem verpflichtenden Gesellschaftsdienst betroffen? Könnten diese einen Fachkräftemangel in bestimmten Sektoren entgegenwirken? Ist die aktive Sterbehilfe in Deutschland legal? Wie läuft eine aktive Sterbehilfe ab?</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0.7334884405136108</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.7614462971687317</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.7494557499885559</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.7483764290809631</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.7285335063934326</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>383</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Schreibe mir stichwortartig die Meinung der deutschen Gesellschaft zum Thema: Waffenlieferung an die Ukraine. Nenne außerdem Vor- und Nachteile. Was umfassen Gesellschaftsdienstaufgaben und inweiweit könnten sie nützlich sein für Gesellschaft und den Jugendlichen der diese Aufgaben bewältigt Was genau wird in der aktiven Sterbehilfe gemacht und nenne mir vorteile dowie Nachteile für eine Legalisierung. Des weiteren nenne die Orte in denen es Legal ist</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0.6703312397003174</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.7014626860618591</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.6887101531028748</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.6885491609573364</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6827900409698486</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>387</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Hältst du es für vertretbar, dass Deutschland Waffen an die Ukraine liefert? Nenne Argumente dafür und dagegen, wäge ab und begründe deine Entscheidung. Was für Möglichkeiten gäbe es für einen verpflichtenden Gesellschaftsdienst für junge Menschen? Begründe, ob man einen verpflichtenden Gesellschaftsdienst für junge Menschen einführen sollte und nenne Vor und Nachteile. Was sind Argumente für oder gegen eine Legalisierung aktiver Sterbehilfe? Wieso sollte aktive Sterbehilfe legalisiert werden? Findest du, dass es sinnvoll wäre, aktive Sterbehilfe zu legalisieren, wenn ja in welchen Fällen. Gib eine Begründung an.</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0.7406513690948486</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.7890297770500183</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.7553662061691284</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7732419967651367</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7426693439483643</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>389</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Welche Gegenargumente gibt es für eine Waffenlieferung und welche Proargumente? Von welchen Gruppen wird besonders die Gegenseite unterstützt? Welche Pro und Kontra Argumente werden in der Diskussion über einen verpflichtenden Gesellschaftsdienst für junge Menschen genannt? Wie viele junge Menschen leisten bereits einen freiwilligen Gesellschaftsdienst? Warum ist die Sterbehilfe in Deutschland verboten? Welche Ethiker haben Texte dazu verfasst? Welche prominenten Fälle der Sterbehilfe gibt es in Deutschland?</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0.7242137789726257</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.7530572414398193</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.7333539128303528</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.7411501407623291</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.7348148226737976</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>392</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Heyy, Deutschland liefert ja immer noch Waffen an die Ukraine. Wieso? eigentlich ist es ja kontraproduktiv für DE wegen Energie und so Hey chat, was ist ein verpflichtender gesellschaftdienst und wird es das in deutschland geben bzw. wieso will man das überhaupt einführen Hey Chat, wann ist die sterbehilfe in deutschland erlaubt und wann nicht, ich weiß nicht so recht was ich davon halten so</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0.6244633793830872</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.6624103188514709</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.6382169723510742</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.646625280380249</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.6492326855659485</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>394</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Bitte nenne in deutschen Medien vertretene Argumente, die für oder gegen deutsche Lieferungen von Waffen in die Ukraine sprechen. Füge jeweils einen Link zur Quelle hinzu und sortiere nach Pro- und Contra-Argumenten. Bitte fasse verschiedene Positionen, die in deutschen Medien zu der Frage vertreten werden, ob ein verpflichtendes Gesellschaftsjahr für junge Menschen in Deutschland eingeführt werden soll, zusammen. Gib zu jeder Position die Quelle an. Bitte erstelle eine Übersicht zu den wichtigsten Argumenten in den deutschen die Medien, die für oder gegen die Legalisierung von aktiver Sterbehilfe sprechen. Gliedere in Pro- und Contra-Argumente und füge jeweils die Quelle hinzu.</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0.6763431429862976</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.7140088081359863</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.7005467414855957</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.7059870362281799</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.6873450875282288</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>396</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Hallo!
+Der russische Angriffskrieg gegen die Ukraine besteht nunmehr seit über vier Jahren. Deutschland steht der Ukraine bei und liefert ihr Waffen sowie militärische Ausrüstung.
+Mir stellt sich vor dem Hintergrund des langanhaltenden, kein Ende nehmenden Krieges die Frage, inwiefern diese militärische Unterstützung noch gerechtfertigt ist. Bringt sie überhaupt etwas? Die Geldausgaben Deutschlands steigen stetig aufgrund dieser militärischen Unterstützung. Ist dies noch vertretbar?
+Bitte hilf mir bei der Beantwortung dieser Fragen und erstellte mir eine Pro-Kontra-Liste der deutschen Waffenlieferung an die Ukraine. Hallo! 
+Aktuell wird kontrovers diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen in Deutschland eingeführt werden sollte. Dieser könnte sozial, ökologisch oder militärisch ausgerichtet sein.
+Ich (Studentin, 20 Jahre alt) bin mir selbst noch nicht ganz im Klaren darüber, wie ich zu dieser Frage stehe. Bitte erstelle mir eine Pro-Kontra-Liste zu dieser Kontroverse, sodass ich mir ein eigenes Meinungsbild schaffen kann. Hallo!
+Ich beschäftige mich mit der Frage, ob die aktive Sterbehilfe in Deutschland legalisiert werden sollte. 
+Wenn der Leidensdruck eines Menschen bspw. aufgrund einer unheilbaren Krankheit hoch ist, er dadurch auch psychisch stark belastet ist, nur palliativ und nicht kurativ behandelt werden kann und den ausdrücklichen Wunsch äußert, sterben zu wollen - stellt dann die aktive Sterbehilfe nicht die bestmögliche "Behandlung" dieses Menschen dar? Wird er dadurch nicht viel eher von seinem Leiden "erlöst"? Stellt die aktive Sterbehilfe somit nicht eine tragbare Entscheidung dar?
+Wie ist deine Informationsquelle hierzu? Kannst du mir bitte gebündelt Informationen zusammenstellen, auch zu der Frage, wie die aktive Sterbehilfe in anderen Ländern gehandhabt wird? Gab es bereits strafrechtliche Konsequenzen?</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0.7517254948616028</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.7833744883537292</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.761147677898407</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.7698366641998291</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.762434184551239</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>397</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Hey, sollte deutschland weiterhin waffen an die Urkaine liefern? Nenne mir pro und contra Argumente Sollte der Werdienst in Deutschland erneut eingeführt werden? was sind Hürden für die Wiedereinführung? Was sind pro und contra Argumente für die aktive Sterbehilfe? Würden sich mehr Menschen suizidieren, wenn Sterbehilfe legal wäre?</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0.7016283869743347</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.7451819181442261</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.7219239473342896</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.7338277697563171</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.7010844349861145</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>398</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>eit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert.
+verschärft eine waffenlieferung die lage?
+was würde passieren wenn deutschland keine waffen mehr liefert?
+Was passiert wenn deutschlandn weiterhin waffen liefert? In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden.
+Nenne mir Vor und nachteile eines solchen gesellschaftsdienst
+was muss man da genau machen ?
+Hälst du es für sinnvoll einen solchen Gesellscahftsdienst als junger mensch zu machen In Deutschland ist die aktive Sterbehilfe (Tötung auf Verlangen) verboten. Es wird jedoch immer wieder diskutiert, ob sie unter bestimmten Bedingungen legalisiert werden sollte — etwa bei unheilbaren Krankheiten und auf ausdrücklichen Wunsch der betroffenen Person.
+Warum ist sterbehilfe verboten während sie in anderen ländern erlaubt ist?</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>0.7746145129203796</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.8014874458312988</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.7759661078453064</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.7878007292747498</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.7689068913459778</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>400</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Gib mir an, wann du zuletzt trainingsdaten gefüttert bekommen hast. ich habe eine Frage zu einem aktuellen Thema, das du kennen solltest. Seit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Erstelle mir eine Tabelle/Argumente; Pro-Contra. Gib ihnen eine Gewichtung anhand folgender Kriterien: Machbarkeit/technische Umsetzung in Deutschland, Zustimmung aus aktuellen Umfragen im Deutschen Volk. Kennzeichne mit Quellen und erfinde keine Zahlen. Verzichte auf redundante Antowrten und schließe verschiedene Perspektiven mitein wie z.B. ethische Argumente, technische Argumente sowie die Perspektive der Ukraine. Beziehe dich auch auf Mögliche Konsequenzen seitens der Ukraine, Russland, USA, der EU und China. In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden.
+Erstelle mir eine Konzept-Map oder gib Schlagwörter für eine solche vor. Ich will wissen welche Aspekte neben politischer, Bundeshaushalts-fragen, Krankenversicherungs-Dilemmata und der Perspektive von jungen Menschen in Deutschland noch so existieren. Du kannst die Begriffe gerne als Anhaltspunkt nehmen aber hänge dich nicht dran auf. Mir geht es um Konzepte jenseits der mir bekannten. In Deutschland ist die aktive Sterbehilfe (Tötung auf Verlangen) verboten. Es wird jedoch immer wieder diskutiert, ob sie unter bestimmten Bedingungen legalisiert werden sollte — etwa bei unheilbaren Krankheiten und auf ausdrücklichen Wunsch der betroffenen Person. Erstelle mir Pro- und Contra Argumente in einer Tabelle und vermeide redundante Antworten. Schließe Aspekte von Medizinischer Machbarkeit, Zugänglichkeit, Missbrauchspotential und Religiöse Motive mitein. Suche außerdem nach Ländern, in denen aktive Sterbehilfe bereits legalisiert ist und beziehe Pro- und Kontraargumente aus den Erfahrungsberichten mitein. Gibt Quellen an.</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7624360918998718</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.7987318634986877</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.7814647555351257</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.7864858508110046</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.7702764272689819</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>402</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Seit Beginn des russischen Angriffskriegs gegen die Ukraine im Februar 2022 liefert Deutschland Waffen und militärische Ausrüstung an die Ukraine. Dieses Vorgehen wird in der deutschen Öffentlichkeit kontrovers diskutiert.
+Wie gerechtfertigt ist diese Aufruhe in Deutschland? In Deutschland wird diskutiert, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden.
+Wie sinnvoll denkst du ist dieser Gesellschaftsdienst? Nenne vor- und Nachteile. In Deutschland ist die aktive Sterbehilfe (Tötung auf Verlangen) verboten. Es wird jedoch immer wieder diskutiert, ob sie unter bestimmten Bedingungen legalisiert werden sollte — etwa bei unheilbaren Krankheiten und auf ausdrücklichen Wunsch der betroffenen Person. 
+Denkst du aktive Sterbehilfe ist moralisch vertretbar? Nenne Pro und Contra Argumente.</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0.7569292187690735</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.7907926440238953</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.7634971737861633</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.7784759998321533</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.7557647824287415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>415</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sollte Deutschland bezüglich des Ukraine-Kriegs weiter Waffen an die Ukraine liefern? Begründe. Gib mir jeweils mindestens 5 Pro- und Contra-Argumente. In Deutschland wird momentan darüber diskutiert, ob ein verpflichtender Gesellschaftsdienst (FSJ, BuFDi oder so) eingeführt werden soll. Gib mir mindestens 5 Argumente dafür und mindestens 5 dagegen. Es wird diskutiert, ob die aktive Sterbehilfe (die in Deutschland momentan verboten ist), erlaubt werden soll. Gib mir mindestens 5 Argumente dafür und mindestens 5 dagegen.</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0.7433289885520935</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.7729295492172241</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.7575446963310242</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.7655657529830933</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.7327558398246765</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>426</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Kannst du eine Übersicht erstellen zu dem Thema Waffenlieferungen in die Ukraine aus Deutschland? Kannst du noch genauer die völkerrechtlichen Probleme betrachten zB. ab welchem Grad der Beteiligung Deutschland auch als Partei des Konflikts gelten würde? Wie genau wäre der angedachte Gesellschaftsdienst für junge Menschen ausgestaltet? Was sind die Argumente der beiden Positionen? Kannst du mir die unterschiedlichen Positionen aufzeigen, die es bei der Diskussion um die aktive Sterbehilfe gibt? Was waren die Argumente des BVerfG den Paragraphen 217 StGB abzuschaffen?</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0.7166833281517029</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.7595617175102234</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.7407385110855103</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.7496934533119202</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.7280215620994568</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>427</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Erstelle eine begründete Stellungnahme dazu, dass Deutschland Waffen an die Ukraine liefert. Erstelle eine begründete Stellungnahme dagegen. Erstelle eine Prognose zur Situation Nenne Vorteile, die dafür sprechen. Nenne Nachteile Erstelle eine begründete Stellungnahme Nenne mir sowohl Gründe, die für eine aktive Sterbehilfe sprechen, als auch Gründe, die dagegen sprechen. Suche Fakten heraus z.B. wie die aktive Sterbehilfe in anderen Ländern aussieht Nenne konkrete Fälle</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7761504054069519</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.8203314542770386</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.7885597348213196</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.8058941960334778</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.7876147627830505</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>430</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Kannst du mir Argumente für und gegen die Lieferung deutscher Waffen an die Ukraine nennen? Liste mir Argumente für und gegen einen verpflichtetenden Gesellschaftsdienst für Junge Menschen auf. Liste mir Argumente für und gegen die Legalisierung von aktiver Sterbehilfe auf.</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0.6777755618095398</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.7062447667121887</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.6949185132980347</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7028663158416748</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.6683246493339539</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>431</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Warum ist es schlecht dass Deutschland Waffen und militärische Ausrüstung an die Ukraine liefert? Wen betrifft ein verpflichtender Gesellschaftsdienst in Deutschland und wie sieht das aus? Gibt es Ausnahmen dass man kein Gesellschaftsdienst machen muss? Welche Parteien sind dafür? Wo ist Sterbehilfe legal? Pro Kontra Sterbehilfe Ist Sterbehilfe mit dem christlichen Glauben vereinbar?</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0.6933114528656006</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.7367608547210693</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.7111339569091797</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.722344696521759</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.6994491815567017</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>432</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Hey Chatgpt, nenn mir mal die Pros und Contras von Waffenlieferungen an die Ukraine Hey Chatgpt, ich habe momentan keine Ahnung wie es um die Wehrdienstdebatte oder einen Gesellschaftsdienst in Deutschland steht. Erklär mir mal, was die Lage und die Pros Contras etc sind. Hey Chatgpt, bitte erklär mir wie die aktuelle Situation mit Sterbehilfe in Deutschland ist und liste mir die Pros und Contras auf</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0.6220854520797729</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.643062949180603</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.6456477046012878</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.6392149925231934</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.6315057277679443</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>445</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Seit 2022 Liefert die BRD Waffen an die Ukraine: wie viel Geld ist dadurch "verloren" gegangen? Ist es sinnvoll ein Land mit Waffen zu Versorgen? Sind wir dann nicht auch Kriegstreiber? Welche Alternativen würde es geben um den Krieg zwischen der Ukraine und Russland zu beenden? Zahlt die Waffenindustrie die in Deutschland produziert eigentlich Steuern? Ich beschäftige mich gerade mit der Debatte um einen verpflichtenden Gesellschaftsdienst in Deutschland. Bevor ich mir eine feste Meinung bilde, brauche ich einen Überblick: Was genau sind die aktuellen Vorschläge (Dauer, Bereiche wie Soziales/Bundeswehr)? Welche rechtlichen Hürden, zum Beispiel bezüglich des Grundgesetzes (Zwangsarbeitsverbot), gibt es da überhaupt? Gib mir bitte eine kurze, strukturierte Zusammenfassung. Lass uns tiefer in die Argumente einsteigen. Ich möchte die Debatte besser verstehen. Erstelle mir eine Übersicht mit den stärksten Pro- und Contra-Argumenten. Berücksichtige dabei bitte verschiedene Perspektiven: Was bringt es der Gesellschaft (z.B. sozialer Zusammenhalt, Entlastung der Pflege)? Was bedeutet es für die betroffenen jungen Menschen (z.B. Orientierung vs. Eingriff in die Lebensplanung)? Und wie sieht es mit den Kosten für den Staat aus? Ich schwanke noch in meiner Position. Einerseits finde ich den Gedanken gut, dass man der Gesellschaft etwas zurückgibt und den Zusammenhalt stärkt. Andererseits widerstrebt mir der Zwang und die zusätzliche Belastung für junge Leute nach der Schule. Spiele mal für mich den kritischen Sparringspartner: Stell mir drei gezielte Fragen, die mir helfen herauszufinden, wo ich ethisch und praktisch die Prioritäten setze. Erkläre mir welchen Formen es von aktiver Sterbehilfe es gibt. Warum darf der Eigentümer eines Tieres über dessen Sterbehilfe entscheiden, der Mensch selbst aber nicht? Welche ethischen Fragen kommen auf? Du bist seit zwanzig Jahren in der Ethikkomission an einer Universitätklinik: welches ethischen Bedenken hast du bezüglich der aktiven Sterbehilfe? Welche Punkte sprechen jedoch für eine aktive Sterbehilfe? Nutze alle genannten Punkte und verfasse mir einen Podcast welcher über das Thema diskutiert.</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0.7252025008201599</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.7589806914329529</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.742256224155426</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.7469788789749146</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.7417768836021423</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>447</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Warum ist es sinnvoll das Deutschland Waffen an die Ukraine liefert? Was passiert wenn Deutschland keine Waffen mehr an die Ukraine liefter? Welche Nachteile könnte ein verpflichtender Gesellschaftsdienst für junge Menschen dem Staat und jungen Menschen bringen? Was spricht gegen die aktive Sterbehilfe in Deutschland?</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6979429125785828</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.720833957195282</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.7066964507102966</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.7092788815498352</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.6942393779754639</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>451</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>zeige mir einen überblick über die deutschen ausgaben im russisch-ukrainischen krieg, mit jahreszahl, wert, was wurde geliefert, welche firmen
+dazu alle quellenangaben angeben, woher diese werte stammen
+fasse mir zusätzlich zusammen, inwiefern die einzelnen parteien in deutschland für oder gegen die lieferungen sind und jeweils deren hauptargumente auflisten
+ich möchte auch noch wissen, wie die medien darüber berichten, teile mir meinungsgebende institute in die unterschiedlichen fronten ein - erkläre mir genau wie ein verpflichtender gesellschaftsdienst in deutschland laut der jetztigen regierung ablaufen soll
+- beschreibe die sozialen, ökologischen und militärischen auswirkungen, die so ein jahr mit sich bringt
+- berechne genaue finanzielle auswirkungen auf den staat und gesellschaft
+- verfasse eine pro und con liste eines solchen jahres aus der sicht einer mitte bis links stehenden (politisch) person
+immer mit wissenschaftlich bzw. politischen quellen arbeiten, die fundiert veröffentlicht werden - warum ist sterbehilfe in deutschland nicht legal?
+- schreibe alle vor und nachteile auf, die mit aktiver sterbehilfe im zusammenhang stehen
+- welche ideen gibt es, um das gesetz zu reformieren?
+- wie steht die kirche dazu?
+- wie wird aktive sterbehilfe in anderen ländern geregelt?
+- mache eine tabelle, die beschreibt welche parteien in deutschland dagegen und dafür sind</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>0.7539498209953308</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.7923389077186584</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.7766469717025757</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.7810770273208618</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.7607839703559875</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>459</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Hi, wie viel Geld gibt Deutschland für Waffen und Ausrüstung aus, die an die Ukraine geliefert werden? Welche Waffen sendet Deutschland in die Ukraine? Was sind Vor- und Nachteile eines verpflichtenden Gesellschaftsdienstes? Welche Jobbranchen sind in Deutschland besonders unterbesetzt? Wieso? Was sind die Vor- und Nachteile der Sterbehilfe? Wie wird die Sterbehilfe in Ländern legitimiert, in der sie legal ist?</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>0.6603232026100159</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.6901224851608276</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.6687540411949158</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.6733844876289368</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.6650354862213135</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>465</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Warum sollte Deutschland weiterhin Waffen an die Ukraine liefern? Gib mir Argumente für die Frage, ob ein verpflichtender Gesellschaftdienst für junge Menschen nach der Schule eingeführt werden soll. Gib mir Argumente für die Frage, ob aktive Sterbehilfe in Deutschland legalisiert werden soll.</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0.7314537167549133</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.7666875720024109</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.7526419162750244</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.7610039710998535</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.7243627309799194</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>466</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Was würde passieren wenn Deutschland keine Waffen mehr in die Ukraine liefert? Was sind die Vor- und Nachteile von einem verpflichtenden Gesellschaftsdienst? Warum ist die sterbehilfe in Deutschland noch nicht legalisiert?</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>0.6299470067024231</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.6687713265419006</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.6385573744773865</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.6511402726173401</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.6348601579666138</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>471</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Was spricht dagegen  und dafür dass Deutschland Waffen an die Ukraine liefert. Stichpunktartig. Même mir Argumente für und gegen Wehrpflicht in Deutschland. stichpunktartig. Sterbehilfe- Argumente</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0.6746717095375061</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.7148579359054565</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.6923857927322388</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.7067530155181885</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.670576274394989</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>475</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Stelle mir wichtige Informationen zu den deutschen Waffenlieferungen in die Ukraine zusammen. Gebe mir für jede Information die Quelle an. Verwende primär seriöse Quellen. Verfasse mir eine Pro/Contra-Liste zu der Frage, ob Deutschland weiter Waffen in die Ukraine liefern sollte. Stelle mir Informationen über den verpflichtenden Gesellschaftsdienst für junge Menschen zusammen. Nutze nur seriöse Quellen und gib diese an. Verfasse eine Pro/Contra-Liste, ob es einen verpflichtenden Gesellschaftsdienst in Deutschland geben sollte Stelle mir verschiedene Informationen zur aktiven Sterbehilfe in Deutschland zusammen, damit ich mir einen Überblick über die Thematik verschaffen kann. Geb stets die Quellen der Informationen an und nutze primär seriöse Quellen. Verfasse mir eine Pro/Contra-Liste zur Legalisierung der aktiven Sterbehilfe.</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0.7109507918357849</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.7406637072563171</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.7351042032241821</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.7349593639373779</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.7084063291549683</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>476</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deutschland liefert momentan Waffen an die Ukraine. Mit welchem Hintergrund und welcher Begründung? Was wären Konsequenzen der Waffenlieferung und wie was passiert, wenn es aufhört? Was beinhaltet ein Gesellschaftsdienst in Deutschland, wie lange hält er an und welche Vor- bzw. Nachteile gibt es? Was spricht für/gegen einen verpflichtenden Gesellschaftsdienst? Sterbehilfe in Deutschland ist ja noch verboten. Welche Gründe gibt es dafür? Was spricht dagegen? Wie wird die Sterbehilfe in anderen Ländern gehandhabt?</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0.6828002333641052</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.7222874164581299</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.6950049996376038</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.7059686183929443</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.6904165744781494</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>478</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>In was für einem waffenwert liefert deutschland der ukraine waffen? Inwieweit hilft der ukraine die Unterstützung deutscher waffen? Welche möglichkeiten gäbe es, wenn in deutschland ein verpflichteter gesellschaftsdienst eingeführt werden würde? Welche vor- oder nachteile bereitet es? Wie labge müsste es mindestens andauern? Gibt es eine statistik die zeigt wie hoch tatsächlich die zahl der verlangenden nach dem tod ist</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>0.684204638004303</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.7084671854972839</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.6888254880905151</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.6926142573356628</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.6854086518287659</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>479</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Aus welchen Gründen  liefert Deutschland waffen an die ukraine Könnte Deutschland auch mit anderen Mitteln helfen? Erstelle eine Tabelle mit vor und Nachteilen Wie könnte dieses Gesellschaftsblatt ganz individuell aussehen? In welchen Ländern auf der Welt ist aktive sterbehilfe erlaubt? Wie viele Menschen ungefähr würden den Zugang zu aktiver sterbehilfe in Deutschland nutzen wollen Gibt es Studien über die Aussagekraft der Entscheidung und ob diese im Nachhinein doch revidiert werden würde</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>0.7376436591148376</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.7764933705329895</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.7524802684783936</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.7603319883346558</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.752020537853241</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>486</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Sollte Deutschland weiterhin Waffen an die Ukraine im jetztigen Krieg, der seit 2022 ist, liefern Zeige mir mehrere Argumente auf warum es gut oder schlecht sein sollte in Deutschland ein verpflichtender Gesellschaftsdienst für junge Menschen einzuführen. Dieser könnte soziale, ökologische oder militärische Aufgaben nach dem Schulabschluss zb. umfassen Wie sollte man zur Legalisierung aktiver Sterbehilfe in Deutschland stehen? Wie ist es mit der Legalisierung aktiver Sterbehilfe in Deutschland? Ist es gut oder schlecht?</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0.6956952810287476</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.7302132248878479</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.719026505947113</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.7214117646217346</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.6902379393577576</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>488</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Nenne mir Vor- und Nachteile der Waffenlieferung von Deutschland an die Ukraine. Gehe auch auf die Konsequenzen ein. Warum sollte in Deutschland kein verpflichtender Gesellschaftsdienst eingeführt werden und welche Alternativen gibt es? Nenne mir Vor- und Nachteile der aktiven Sterbehilfe. Gehe bei den Nachteilen darauf ein, wie es in den anderen Ländern legitimiert wird.</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>0.6549059152603149</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.6949635148048401</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.672231137752533</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.6797307729721069</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.6563420295715332</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>489</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Welche Waffen schickte Deutschland seit Beginn des Ukraine-Krieges an die Ukraine? Welche Auswirkungen hatten diese Waffen bis jetzt? WIe würde ein verpflichtender Gesellschaftsdienst in Deutschland für junge Menschen aussehen? Kann man selbst entscheiden, wo man diesen Dienst leisten will? Was bekommt man dafür? Erzähle mir etwas über die Legalisierung der Sterbehilfe in Deutschland Was wären die Konsequenzen einer legalen aktiven Sterbehilfe?</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0.7684565782546997</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.7856966257095337</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.771017849445343</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.7774083018302917</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.765363335609436</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>491</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Liste mir Argumente, die für und gegen die Lieferung deutscher Waffen an die Ukraine sprechen. Welche Argumente fallen häufig in der Diskussion darüber, dass Deutschland Waffen in die Ukraine liefert? (Hintergrundabschnitt als Kontextinformation einfügen)
+Kannst du mir hierzu Pro- und Contra-Argumente auflisten? Liste mir Pro- und Contra-Argumente zum Thema aktive Sterbehilfe in Deutschland Was spricht für und was gegen eine aktive Sterbehilfe in Deutschland?</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0.6758304834365845</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.707048237323761</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.6962190866470337</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.700090765953064</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.6743497848510742</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>492</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Was ist Imperialismus und warum werden Kriege in erster Linie geführt und wie beendet man Kriege? Indem man mehr Waffen schickt? Nenne 3Gründe gegen Militärdienst Gründe für und gegen Sterbehilfe</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>0.7501804828643799</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.7630513310432434</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.7426385283470154</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.7583485841751099</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.7315433621406555</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>493</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Warum sollte Deutschland Waffen an die Ukraine liefern? Wem hilft das wirklich? Was sind die Gründe dagegen? Gehe auch auf Punkte zu Sozialabbau  und dem Zusammenhang mit Militariesierung ein. Nehme eine Imperialistische Haltung ein, beim beantworten der Frage. Was sind die Vor- und Nachteile eines Gessellschaftdienstes für junge Menschen, vor allem  für soziole und ökologische Aufgabenbereiche? was spricht gegen ein militär dienst? was für Regelungungen für sterbehilfe könnte es geben das dieser sinnvoll umgesetzt werden kann und im Interesse der erkrankten Personen steht? wie sehen die Meinungen von Expert*innen zu diesem Thema aus?</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0.7099509239196777</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.7429490685462952</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.7257086038589478</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.7304227948188782</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.7191982865333557</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>503</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Welche Argumente sprechen für und gegen eine Waffenlieferung an die Ukraine? Gibt es andere wirksame Möglichkeiten, die Ukraine zu unterstützen ohne sie mit Waffen zu versorgen? Welche Argumente sprechen für und gegen einen verpflichtenden Gesellschaftsdienst für junge Menschen in Deutschland? Erstelle mir eine Liste mit Argumenten für und gegen die Legalisierung von Sterbehilfe in Deutschland</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>0.6974660754203796</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.727175235748291</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.70939701795578</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.717576801776886</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.6881545186042786</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>504</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Was sind Gründe für und dagegen dass Deutschland Waffen an die Ukraine liefert? Warum liefert Deutschland Waffen an die Ukraine? Wer ist dafür dass Deutschland weiter Waffen an die Ukraine liefert? Wieso sollte es einen verpflichtenden Gesellschaftsdienst in Deutschland geben? Was wären Auswirkungen, wenn es diesen geben würde? Was wären Gefahren wenn es diesen geben würde? Was sind Gründe für und gegen die Legalisierung von aktiver Sterbehilfe in Deutschland? Wie ist das in anderen Ländern, wie hat sich die Legalisierung dort ausgewirkt?</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>0.6841078400611877</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.7150049209594727</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.6939129829406738</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.7017356753349304</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.6854402422904968</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>505</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Nenne mir alle Gründe, warum Länder Waffen und militärische Ausrüstung an Kriegsparteien liefern. Nenne mir Vor- und Nachteile dafür, dass Deutschland Waffen und militärische Ausrüstung an die Ukraine liefert. Nenne mir außerdem Vor- und Nachteile dafür, warum Länder generell Waffen und militärische Ausrüstung an Kriegsparteien liefern.
+Gib mir für deine Informationen Belege mit Quellen, die tatsächlich existieren. Erfinde nichts selbst hinzu. Arbeite wissenschaftlich Nenne mir Vor- und Nachteile für einen verpflichtenden Gesellschaftsdienst für junge Menschen in Deutschland. Ich bin mir unsicher, ob ein verpflichtender Gesellschaftsdienst für junge Menschen eingeführt werden soll. Dieser könnte soziale, ökologische oder militärische Aufgaben umfassen und z.B. nach dem Schulabschluss geleistet werden. Hilf mir, meine Einstellung zu dem Thema herauszufinden. Stelle mir dafür Fragen. Was ist die derzeitige Rechtsgrundlage bei Sterbehilfe in Deutschland, insbesondere aktiver Sterbehilfe? Wie kam es zur aktuellen Rechtslage? Welche Argumente gibt es für eine Legalisierung? Nenne mir diese Argumente, und analysiere sie auf ihre Stichhaltigkeit Was ist die derzeitige Rechtsgrundlage bei Sterbehilfe in Deutschland, insbesondere aktiver Sterbehilfe? Nenne mir Vor- und Nachteile der Legalisierung aktiver Sterbehilfe. Nenne Quellen, die es auch tatsächlich gibt</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>0.749131977558136</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.7818035483360291</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.7611768841743469</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.7701413035392761</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.7434743046760559</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>506</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Seit Beginn des Ukraine Kriegs liefert Deutschland Waffen und ähnliches an die Ukraine zu unterstützen. Ich versteh das man der Ukraine helfen möchte, aber ich weiß nicht genau ob ich es so gut finde wenn man ihnen einfach Waffen zur Verfügung stellt oder ob man nicht eher anders helfen sollte. Was gäbe für Alternative Hilfsmöglichketen und was sagen Experten sind für und wieder von Waffenlieferungen? Es wird gerade diskutiert ob es in Deutschland ein verpflichtenden Gesellschaftsdienst geben soll. Ich finde die Idee eigentlich gut, versteh aber auch wenn Leute dagegen sind. Was sind aktuelle Pro und Contra für dieses Thema? In Deutschland wird ja immer darüber diskutiert ob aktive Sterbehilfe legalisiert werden soll. Ich bin bei der Frage noch unentschlossen. Kannst du mir helfen die Pro und Contra von aktiver Sterbehilfe zu verstehen, sodass ich mehr darüber weiß?</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>0.6877025365829468</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.7232961058616638</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.7074164748191833</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.7119918465614319</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.7085083723068237</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>517</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Deutschland liefert, wie andere Länder auch, Waffen an die Ukraine seit Beginn des Angriffkriegs von russicher Seite. Was sind Argumente für und gegen die Waffenlieferungen an die Ukraine? In Deutschland wird aktuell ein verpflichtender Gesellschaftsdienst für junge Menschen diskutiert. Was für Vorteile oder Nachteile könnte die Umsetzung haben? Wie könnte ein solcher Dienst aussehen und in welchen Bereichen könnte er umgesetzt werden? Ich setze mich der Fragestellung auseinander, ob die aktive Sterbehilfe in Deutschland legalisiert werden sollte. Was sind pro und contra Argumente? In welchen Ländern ist die aktive Sterbehilfe legal und unter welchen Bedingungen?</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>0.6936519145965576</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.7324774861335754</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.7110781073570251</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.7188529372215271</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.701145350933075</v>
       </c>
     </row>
   </sheetData>
